--- a/src/attributions/attributions_saliency_traj_337.xlsx
+++ b/src/attributions/attributions_saliency_traj_337.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.428280822641682e-05</v>
+        <v>6.751176442776341e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0001170867835753597</v>
+        <v>2.799180492729647e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.322217030974571e-05</v>
+        <v>2.663232407940086e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.686884206719697e-05</v>
+        <v>2.371365098952083e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.885937308543362e-05</v>
+        <v>5.0481821745052e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001311467058258131</v>
+        <v>1.041536052071024e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.955728061555419e-06</v>
+        <v>3.974842002207879e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>6.100883183535188e-06</v>
+        <v>2.894500994443661e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>8.878991138772108e-06</v>
+        <v>1.191071987705072e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.704835373559035e-05</v>
+        <v>4.970086592948064e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>8.850666927173734e-05</v>
+        <v>7.518867278122343e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.77833373224712e-06</v>
+        <v>2.694149770832155e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>8.541208444512449e-06</v>
+        <v>1.056222799888928e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.311492269451264e-05</v>
+        <v>1.194196102005662e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.722872346173972e-05</v>
+        <v>9.529015187581535e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>7.882402314862702e-06</v>
+        <v>6.433969247154891e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.361343624419533e-05</v>
+        <v>2.705344513742602e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>2.777756162686273e-05</v>
+        <v>1.65788299000269e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>7.730004654149525e-06</v>
+        <v>2.225385514975642e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>9.91740762401605e-06</v>
+        <v>5.356152087188093e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.300452357914764e-06</v>
+        <v>2.679327280930011e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.002134558802936e-05</v>
+        <v>3.783862666750792e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>2.556842446210794e-05</v>
+        <v>7.870531590015162e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.312141830567271e-05</v>
+        <v>6.963793566683307e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.060091290128184e-05</v>
+        <v>2.072211373160826e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.309203854470979e-06</v>
+        <v>7.352358579737484e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.011851054499857e-06</v>
+        <v>8.819375807433971e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.102723126678029e-05</v>
+        <v>9.733764727570815e-08</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.263778924316284e-06</v>
+        <v>1.559567408548901e-08</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.253502867068164e-06</v>
+        <v>2.899560968216974e-06</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.126315277768299e-05</v>
+        <v>9.136531389231095e-07</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.254540206398815e-05</v>
+        <v>8.480144515488064e-07</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.576050453877542e-05</v>
+        <v>6.097715754549426e-08</v>
       </c>
       <c r="AH4" t="n">
-        <v>9.447071533941198e-07</v>
+        <v>1.164661625807639e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.000495649350341e-05</v>
+        <v>3.376585937076015e-06</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.833663756973692e-07</v>
+        <v>5.860205192220747e-07</v>
       </c>
       <c r="AK4" t="n">
-        <v>7.914563866506796e-07</v>
+        <v>7.261726295837434e-07</v>
       </c>
       <c r="AL4" t="n">
-        <v>7.592057954752818e-06</v>
+        <v>2.150823377178313e-07</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.698818778095301e-05</v>
+        <v>2.025063849941944e-08</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.335419983661268e-05</v>
+        <v>3.228759624107624e-06</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.723749952972867e-06</v>
+        <v>4.370112947071902e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.552877776906826e-05</v>
+        <v>1.776433578015713e-06</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.083015351672657e-05</v>
+        <v>5.525717483578774e-07</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.63800323207397e-05</v>
+        <v>8.295281759274076e-07</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.461085725575686e-05</v>
+        <v>1.951831336555188e-06</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.291335689136758e-06</v>
+        <v>1.76042391331066e-07</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.055080691818148e-05</v>
+        <v>1.018627608573297e-05</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.385203308425844e-05</v>
+        <v>1.883108552647172e-06</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.68864754011156e-06</v>
+        <v>1.092627144316793e-06</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.14589693112066e-05</v>
+        <v>1.717615987217869e-07</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.578631731215864e-05</v>
+        <v>4.622668711817823e-06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.288761945441365e-05</v>
+        <v>3.140222588626784e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.136382686847355e-06</v>
+        <v>5.300623342918698e-06</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.287769454298541e-05</v>
+        <v>6.411557933461154e-07</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.483455995796248e-05</v>
+        <v>5.178259470994817e-06</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.332859185116831e-05</v>
+        <v>3.34010678670893e-07</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.452571177651407e-05</v>
+        <v>1.447759359507472e-06</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.903916644456331e-06</v>
+        <v>1.969309323612833e-06</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.023807221325114e-05</v>
+        <v>2.319869736311375e-06</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.05800851189997e-05</v>
+        <v>2.18933428186574e-06</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.009270949405618e-05</v>
+        <v>1.294173671340104e-06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.78615482582245e-05</v>
+        <v>5.829540441482095e-06</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.013564466731623e-05</v>
+        <v>9.824854032558505e-07</v>
       </c>
       <c r="BL4" t="n">
-        <v>3.207853296771646e-06</v>
+        <v>1.741846062941477e-06</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.139162122854032e-05</v>
+        <v>2.654843683558283e-06</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.060682163573802e-06</v>
+        <v>3.012085301179468e-07</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.158080173510825e-06</v>
+        <v>1.806537511583883e-06</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.954094295797404e-05</v>
+        <v>1.238674485648517e-06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.460092789784539e-06</v>
+        <v>1.892930072244781e-06</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.734872785164043e-05</v>
+        <v>2.605475629025022e-06</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.951844054332469e-06</v>
+        <v>1.392634544572502e-06</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.174991646432318e-06</v>
+        <v>7.951831548780319e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.186610552394995e-05</v>
+        <v>1.526360165371443e-06</v>
       </c>
       <c r="BV4" t="n">
-        <v>2.956576099677477e-05</v>
+        <v>1.98156442365871e-07</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.884639459603932e-05</v>
+        <v>2.848211352102226e-06</v>
       </c>
       <c r="BX4" t="n">
-        <v>9.490992852079216e-06</v>
+        <v>6.73736121825641e-06</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.759526432782877e-05</v>
+        <v>5.813189545733621e-06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.577745469054207e-06</v>
+        <v>7.643458957318217e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.255436584164272e-07</v>
+        <v>4.312822738938848e-07</v>
       </c>
       <c r="CB4" t="n">
-        <v>1.6291282918246e-06</v>
+        <v>6.973901918172487e-07</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.010222669923678e-05</v>
+        <v>1.946209295056178e-06</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.101480160694337e-06</v>
+        <v>1.363585738545225e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.512626386102056e-05</v>
+        <v>1.299492737416585e-06</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.18777716124896e-05</v>
+        <v>4.992098752154561e-07</v>
       </c>
       <c r="CG4" t="n">
-        <v>5.103796866023913e-06</v>
+        <v>1.438347680959851e-06</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.050319133355515e-05</v>
+        <v>1.592553644513828e-07</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.379600846325047e-05</v>
+        <v>2.799688218146912e-06</v>
       </c>
       <c r="CJ4" t="n">
-        <v>7.428572644130327e-06</v>
+        <v>7.218785640361602e-07</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.799894562282134e-07</v>
+        <v>1.420933131157653e-06</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.6009907994885e-05</v>
+        <v>7.529032473030384e-07</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.062617138813948e-05</v>
+        <v>2.035337161032658e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.020850297412835e-05</v>
+        <v>4.121340225538006e-06</v>
       </c>
       <c r="CO4" t="n">
-        <v>2.36988635151647e-05</v>
+        <v>5.216739964453154e-07</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.544375845696777e-05</v>
+        <v>1.006850993690023e-06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>8.790410902292933e-06</v>
+        <v>8.623572966826032e-07</v>
       </c>
       <c r="CR4" t="n">
-        <v>4.103372930330806e-07</v>
+        <v>3.538494638632983e-06</v>
       </c>
       <c r="CS4" t="n">
-        <v>8.664692359161563e-06</v>
+        <v>3.416333584027598e-06</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.693942406040151e-06</v>
+        <v>2.065079797830549e-06</v>
       </c>
       <c r="CU4" t="n">
-        <v>3.10347240883857e-05</v>
+        <v>1.018334842228796e-06</v>
       </c>
       <c r="CV4" t="n">
-        <v>6.95307335263351e-07</v>
+        <v>1.620476382413472e-06</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.912603875098284e-05</v>
+        <v>8.36336937481974e-07</v>
       </c>
       <c r="CX4" t="n">
-        <v>8.830310434859712e-06</v>
+        <v>7.025604986665712e-08</v>
       </c>
       <c r="CY4" t="n">
-        <v>7.310777164093452e-06</v>
+        <v>1.280887204302417e-06</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.188399892271264e-05</v>
+        <v>4.764519303535053e-07</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.27551627176581e-05</v>
+        <v>2.226173592134728e-06</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.894129920605337e-06</v>
+        <v>7.613573416165309e-07</v>
       </c>
       <c r="DC4" t="n">
-        <v>4.005427399533801e-06</v>
+        <v>8.634054893263965e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.48569106386276e-05</v>
+        <v>1.059825649463164e-08</v>
       </c>
       <c r="DE4" t="n">
-        <v>4.0889417505241e-06</v>
+        <v>2.542238917158102e-06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.465046079829335e-05</v>
+        <v>3.191940550095751e-06</v>
       </c>
       <c r="DG4" t="n">
-        <v>9.489270269114058e-06</v>
+        <v>4.098333761248796e-07</v>
       </c>
       <c r="DH4" t="n">
-        <v>3.815905802184716e-05</v>
+        <v>8.420412882514938e-07</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.244605118699837e-05</v>
+        <v>1.606207888471545e-06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>5.781569416285492e-05</v>
+        <v>3.201374738637242e-06</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.450181247899309e-05</v>
+        <v>1.361321437798324e-06</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.038368463923689e-05</v>
+        <v>1.184144821309019e-06</v>
       </c>
       <c r="DM4" t="n">
-        <v>4.881379936705343e-05</v>
+        <v>1.56020064423501e-06</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.341480492556002e-05</v>
+        <v>4.640440920411493e-08</v>
       </c>
       <c r="DO4" t="n">
-        <v>8.269801583082881e-06</v>
+        <v>4.037854921534745e-07</v>
       </c>
       <c r="DP4" t="n">
-        <v>5.319729098118842e-06</v>
+        <v>3.117999767709989e-06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.434322439308744e-05</v>
+        <v>4.035028723592404e-06</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.461008105252404e-05</v>
+        <v>2.474042048561387e-06</v>
       </c>
       <c r="DS4" t="n">
-        <v>8.707548659003805e-06</v>
+        <v>3.42348835147277e-06</v>
       </c>
       <c r="DT4" t="n">
-        <v>2.481380943208933e-05</v>
+        <v>1.956968390004477e-06</v>
       </c>
       <c r="DU4" t="n">
-        <v>3.526610271364916e-06</v>
+        <v>2.108622084051603e-06</v>
       </c>
       <c r="DV4" t="n">
-        <v>8.593877282692119e-06</v>
+        <v>9.554888720231247e-07</v>
       </c>
       <c r="DW4" t="n">
-        <v>8.97898462426383e-06</v>
+        <v>2.247601059934823e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.917292118188925e-06</v>
+        <v>2.263104306621244e-06</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.439668247068767e-07</v>
+        <v>3.344596962051583e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.53886991131003e-06</v>
+        <v>1.17462070647889e-06</v>
       </c>
       <c r="EA4" t="n">
-        <v>6.4879145611485e-06</v>
+        <v>2.548423935877508e-06</v>
       </c>
       <c r="EB4" t="n">
-        <v>4.155972419539467e-06</v>
+        <v>1.166086349257967e-06</v>
       </c>
       <c r="EC4" t="n">
-        <v>6.719702923874138e-06</v>
+        <v>8.20247123556328e-07</v>
       </c>
       <c r="ED4" t="n">
-        <v>1.328981943515828e-05</v>
+        <v>2.352022647755803e-06</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.37764000101015e-05</v>
+        <v>1.655733854022401e-06</v>
       </c>
       <c r="EF4" t="n">
-        <v>3.382926024642074e-06</v>
+        <v>2.249057843073388e-06</v>
       </c>
       <c r="EG4" t="n">
-        <v>1.207535387948155e-05</v>
+        <v>1.862416070252948e-06</v>
       </c>
       <c r="EH4" t="n">
-        <v>4.534099844022421e-06</v>
+        <v>1.720388127068873e-06</v>
       </c>
       <c r="EI4" t="n">
-        <v>2.192437204939779e-05</v>
+        <v>1.500286657574179e-06</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.573255576658994e-05</v>
+        <v>2.330300958419684e-06</v>
       </c>
       <c r="EK4" t="n">
-        <v>6.554963874805253e-06</v>
+        <v>2.167828597521293e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.465457535232417e-05</v>
+        <v>1.089209149540693e-07</v>
       </c>
       <c r="EM4" t="n">
-        <v>2.722263161558658e-06</v>
+        <v>6.601455879717832e-07</v>
       </c>
       <c r="EN4" t="n">
-        <v>5.025490281695966e-06</v>
+        <v>8.758071317060967e-07</v>
       </c>
       <c r="EO4" t="n">
-        <v>1.062983210431412e-05</v>
+        <v>1.072951590685989e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.716172730288235e-06</v>
+        <v>8.345631385964225e-07</v>
       </c>
       <c r="EQ4" t="n">
-        <v>3.381890110176755e-06</v>
+        <v>2.881685077227303e-06</v>
       </c>
       <c r="ER4" t="n">
-        <v>6.585873961739708e-06</v>
+        <v>8.596059615229024e-07</v>
       </c>
       <c r="ES4" t="n">
-        <v>3.399440902285278e-05</v>
+        <v>8.993703772830486e-07</v>
       </c>
       <c r="ET4" t="n">
-        <v>4.536858614301309e-05</v>
+        <v>4.286849616619293e-06</v>
       </c>
       <c r="EU4" t="n">
-        <v>2.035199395322707e-05</v>
+        <v>1.555539483888424e-06</v>
       </c>
       <c r="EV4" t="n">
-        <v>1.834849717852194e-05</v>
+        <v>1.48938340771565e-07</v>
       </c>
       <c r="EW4" t="n">
-        <v>2.539905290177558e-05</v>
+        <v>9.003674961149954e-08</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.222934429279121e-06</v>
+        <v>2.109212800860405e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>1.884481389424764e-05</v>
+        <v>1.227911639034573e-06</v>
       </c>
       <c r="EZ4" t="n">
-        <v>3.395321300558862e-06</v>
+        <v>3.680053168864106e-07</v>
       </c>
       <c r="FA4" t="n">
-        <v>2.315664460184053e-08</v>
+        <v>1.585199925102643e-06</v>
       </c>
       <c r="FB4" t="n">
-        <v>1.54228928295197e-05</v>
+        <v>6.727830168529181e-07</v>
       </c>
       <c r="FC4" t="n">
-        <v>1.820214492909145e-05</v>
+        <v>2.736969918260002e-06</v>
       </c>
       <c r="FD4" t="n">
-        <v>1.230138605023967e-05</v>
+        <v>6.927811568857578e-07</v>
       </c>
       <c r="FE4" t="n">
-        <v>5.363732270780019e-06</v>
+        <v>1.136839841819892e-06</v>
       </c>
       <c r="FF4" t="n">
-        <v>2.149778811144643e-05</v>
+        <v>4.924345375911798e-08</v>
       </c>
       <c r="FG4" t="n">
-        <v>5.491999672813108e-06</v>
+        <v>3.576881908884388e-06</v>
       </c>
       <c r="FH4" t="n">
-        <v>1.115080885938369e-05</v>
+        <v>1.541975365171311e-07</v>
       </c>
       <c r="FI4" t="n">
-        <v>8.326011084136553e-06</v>
+        <v>6.74307955250697e-07</v>
       </c>
       <c r="FJ4" t="n">
-        <v>1.716565748210996e-05</v>
+        <v>1.220028025272768e-07</v>
       </c>
       <c r="FK4" t="n">
-        <v>8.020784662221558e-06</v>
+        <v>4.649479706131388e-06</v>
       </c>
       <c r="FL4" t="n">
-        <v>2.063996907963883e-05</v>
+        <v>1.791069962564507e-06</v>
       </c>
       <c r="FM4" t="n">
-        <v>7.050195563351735e-06</v>
+        <v>2.529753828639514e-08</v>
       </c>
       <c r="FN4" t="n">
-        <v>1.005619378702249e-05</v>
+        <v>1.857451479736483e-06</v>
       </c>
       <c r="FO4" t="n">
-        <v>1.817900192691013e-05</v>
+        <v>8.619447839919303e-07</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.430805347510614e-06</v>
+        <v>4.460053332877578e-06</v>
       </c>
       <c r="FQ4" t="n">
-        <v>2.953801413241308e-05</v>
+        <v>3.092949100391706e-06</v>
       </c>
       <c r="FR4" t="n">
-        <v>1.612946107343305e-05</v>
+        <v>1.936831722559873e-06</v>
       </c>
       <c r="FS4" t="n">
-        <v>5.671361577697098e-06</v>
+        <v>1.393588490827824e-06</v>
       </c>
       <c r="FT4" t="n">
-        <v>9.65136041486403e-06</v>
+        <v>1.060228896676563e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>3.819910489255562e-05</v>
+        <v>2.731194172156393e-06</v>
       </c>
       <c r="FV4" t="n">
-        <v>5.985089046589565e-06</v>
+        <v>4.273813829058781e-06</v>
       </c>
       <c r="FW4" t="n">
-        <v>8.862014510668814e-06</v>
+        <v>1.834202521422412e-06</v>
       </c>
       <c r="FX4" t="n">
-        <v>1.911732033477165e-05</v>
+        <v>2.080418653349625e-06</v>
       </c>
       <c r="FY4" t="n">
-        <v>1.957056156243198e-05</v>
+        <v>1.289674287363596e-07</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.903553857118823e-05</v>
+        <v>2.616686970213777e-06</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.971102730953135e-06</v>
+        <v>1.73302839812095e-06</v>
       </c>
       <c r="GB4" t="n">
-        <v>8.622790119261481e-06</v>
+        <v>1.076045009540394e-06</v>
       </c>
       <c r="GC4" t="n">
-        <v>3.175386882503517e-05</v>
+        <v>3.509772568577318e-06</v>
       </c>
       <c r="GD4" t="n">
-        <v>2.621959993120981e-06</v>
+        <v>2.662761971805594e-06</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.037817310134415e-05</v>
+        <v>1.259274654330511e-06</v>
       </c>
       <c r="GF4" t="n">
-        <v>6.19762886344688e-07</v>
+        <v>1.358374561277742e-06</v>
       </c>
       <c r="GG4" t="n">
-        <v>1.333563523076009e-05</v>
+        <v>1.564049512126076e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0001914820459205657</v>
+        <v>0.002788078039884567</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001627280726097524</v>
+        <v>0.0566929467022419</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002019013627432287</v>
+        <v>0.008205443620681763</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008530103368684649</v>
+        <v>0.04351182654500008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001216120086610317</v>
+        <v>0.001543337479233742</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002668938541319221</v>
+        <v>0.001433550845831633</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001789090747479349</v>
+        <v>0.0353928878903389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001580463867867365</v>
+        <v>0.02001403458416462</v>
       </c>
       <c r="I5" t="n">
-        <v>5.481097832671367e-05</v>
+        <v>0.01509684976190329</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001713365782052279</v>
+        <v>0.008321992121636868</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001204375294037163</v>
+        <v>0.05162392184138298</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001906197285279632</v>
+        <v>0.01582394354045391</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001007039332762361</v>
+        <v>0.05946316570043564</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001794825890101492</v>
+        <v>0.02024529315531254</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0004873343859799206</v>
+        <v>0.00638693617656827</v>
       </c>
       <c r="P5" t="n">
-        <v>6.152156856842339e-06</v>
+        <v>0.03178232163190842</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001382084155920893</v>
+        <v>0.002484402153640985</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001322308817179874</v>
+        <v>0.008815358392894268</v>
       </c>
       <c r="S5" t="n">
-        <v>4.682031431002542e-06</v>
+        <v>0.002345854882150888</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003993017307948321</v>
+        <v>0.008877833373844624</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003465474001131952</v>
+        <v>0.0003527506487444043</v>
       </c>
       <c r="V5" t="n">
-        <v>1.518757198937237e-05</v>
+        <v>0.000225104158744216</v>
       </c>
       <c r="W5" t="n">
-        <v>4.973064642399549e-05</v>
+        <v>0.007923235185444355</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004796724824700505</v>
+        <v>0.01226303819566965</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002180622395826504</v>
+        <v>0.005751470103859901</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002551923389546573</v>
+        <v>0.02079512178897858</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.696198837133124e-05</v>
+        <v>0.004072608891874552</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0002293994184583426</v>
+        <v>0.0006972609553486109</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0001750265364535153</v>
+        <v>0.003153362311422825</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002165352925658226</v>
+        <v>0.006700222846120596</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0003100172325503081</v>
+        <v>0.005762016400694847</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.000425706704845652</v>
+        <v>0.006791788153350353</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0001353107509203255</v>
+        <v>0.03264934197068214</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.199798811692744e-05</v>
+        <v>0.003011813852936029</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0001078565401257947</v>
+        <v>0.01373020745813847</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0003226473927497864</v>
+        <v>0.003237649099901319</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001392423582728952</v>
+        <v>0.003256519557908177</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0001575604837853462</v>
+        <v>0.01827456057071686</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001389230747008696</v>
+        <v>0.007735454477369785</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.271978130214848e-05</v>
+        <v>0.004861939698457718</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0005398907233029604</v>
+        <v>0.01156337093561888</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0003044727491214871</v>
+        <v>0.009057453833520412</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.48139986069873e-06</v>
+        <v>0.009000731632113457</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.91741855815053e-05</v>
+        <v>0.0007528710411861539</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.652235368965194e-05</v>
+        <v>0.002952150534838438</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.585953764850274e-06</v>
+        <v>0.0005187304923310876</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001203419174998999</v>
+        <v>0.02100532315671444</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0001421816850779578</v>
+        <v>0.008149036206305027</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.119481334579177e-05</v>
+        <v>0.02076086960732937</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.000235446059377864</v>
+        <v>0.04299568757414818</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0001331550593022257</v>
+        <v>0.01273551117628813</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0001222510036313906</v>
+        <v>0.001960011664777994</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.663002179469913e-05</v>
+        <v>0.001433005905710161</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0006154995644465089</v>
+        <v>0.006557854823768139</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0003455793485045433</v>
+        <v>0.01072085648775101</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0005839493242092431</v>
+        <v>0.002576147671788931</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0005642019677907228</v>
+        <v>0.01024263445287943</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0004485062090680003</v>
+        <v>0.006126264110207558</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001016792375594378</v>
+        <v>0.02138790115714073</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0007053244044072926</v>
+        <v>0.003244457300752401</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0002935910888481885</v>
+        <v>0.0129476822912693</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0001034944652928971</v>
+        <v>0.02823562361299992</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0003116150910500437</v>
+        <v>0.002868353854864836</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0003521356265991926</v>
+        <v>4.779873415827751e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0005282220081426203</v>
+        <v>0.01137849688529968</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.000359851896064356</v>
+        <v>0.006632351316511631</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.000218345521716401</v>
+        <v>0.01025290228426456</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.000660174700897187</v>
+        <v>0.0123742762953043</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.000440903240814805</v>
+        <v>0.001206813380122185</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0001066503100446425</v>
+        <v>0.004919790662825108</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0002655800490174443</v>
+        <v>0.004269063007086515</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0002122914011124521</v>
+        <v>0.009582184255123138</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.504228101926856e-05</v>
+        <v>0.003022750839591026</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0004883118672296405</v>
+        <v>0.01919025182723999</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.716870797798038e-05</v>
+        <v>0.008247965946793556</v>
       </c>
       <c r="BX5" t="n">
-        <v>5.021818287787028e-05</v>
+        <v>0.03190545737743378</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0001620606053620577</v>
+        <v>0.002193860244005919</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0003383551957085729</v>
+        <v>0.008210070431232452</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.674604497267865e-05</v>
+        <v>0.007230011746287346</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001570774475112557</v>
+        <v>0.004150731023401022</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001970894227270037</v>
+        <v>0.002061446197330952</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.800509486813098e-05</v>
+        <v>0.0007689439225941896</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0002859067753888667</v>
+        <v>0.0172327347099781</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.178471913794056e-05</v>
+        <v>0.0005692136473953724</v>
       </c>
       <c r="CG5" t="n">
-        <v>8.012089529074728e-05</v>
+        <v>0.01940944045782089</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.259220339823514e-05</v>
+        <v>0.003052071435377002</v>
       </c>
       <c r="CI5" t="n">
-        <v>4.963318860973231e-05</v>
+        <v>0.00135431659873575</v>
       </c>
       <c r="CJ5" t="n">
-        <v>6.026728078722954e-05</v>
+        <v>0.001896744361147285</v>
       </c>
       <c r="CK5" t="n">
-        <v>2.157170092687011e-05</v>
+        <v>0.0001454743178328499</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0002268355747219175</v>
+        <v>0.002597268205136061</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.00042357636266388</v>
+        <v>0.004631234332919121</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004176095826551318</v>
+        <v>0.002397735603153706</v>
       </c>
       <c r="CO5" t="n">
-        <v>8.509986946592107e-05</v>
+        <v>0.02402969636023045</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0003150765551254153</v>
+        <v>0.03846776112914085</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0005272022099234164</v>
+        <v>0.003248264081776142</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.985463313758373e-05</v>
+        <v>0.01273190136998892</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.990540815517306e-05</v>
+        <v>0.01891568303108215</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0002835852210409939</v>
+        <v>0.01195971295237541</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0001784550113370642</v>
+        <v>0.004983075894415379</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.58275158557808e-05</v>
+        <v>0.0005725575610995293</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.000218614746700041</v>
+        <v>0.01662752591073513</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0001121803143178113</v>
+        <v>0.00222089746966958</v>
       </c>
       <c r="CY5" t="n">
-        <v>7.816439756425098e-05</v>
+        <v>0.02065038681030273</v>
       </c>
       <c r="CZ5" t="n">
-        <v>5.343393786461093e-05</v>
+        <v>0.0002665193751454353</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.866628892661538e-05</v>
+        <v>0.000731882406398654</v>
       </c>
       <c r="DB5" t="n">
-        <v>4.111437010578811e-05</v>
+        <v>0.001242561265826225</v>
       </c>
       <c r="DC5" t="n">
-        <v>5.810954462504014e-05</v>
+        <v>0.0008136764517985284</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0001256202667718753</v>
+        <v>0.0003177451435476542</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.000141954340506345</v>
+        <v>0.001324518583714962</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0004777805297635496</v>
+        <v>0.01446837838739157</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0003647499834187329</v>
+        <v>0.002657377626746893</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0006163448560982943</v>
+        <v>0.02446776628494263</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0005641033058054745</v>
+        <v>0.007963340729475021</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0003420111024752259</v>
+        <v>0.01614460721611977</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.262464765110053e-05</v>
+        <v>0.005156687926501036</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0002624563639983535</v>
+        <v>0.03058122657239437</v>
       </c>
       <c r="DM5" t="n">
-        <v>8.836776396492496e-05</v>
+        <v>0.004338514059782028</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.993431214941666e-05</v>
+        <v>0.001306078978814185</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0001613434869796038</v>
+        <v>0.006869690492749214</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001292033848585561</v>
+        <v>0.001880288124084473</v>
       </c>
       <c r="DQ5" t="n">
-        <v>4.609839379554614e-05</v>
+        <v>0.01161375734955072</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.056929800659418e-06</v>
+        <v>0.0006061828462406993</v>
       </c>
       <c r="DS5" t="n">
-        <v>3.612637374317273e-05</v>
+        <v>0.003027716651558876</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.000279670231975615</v>
+        <v>0.01345456205308437</v>
       </c>
       <c r="DU5" t="n">
-        <v>8.638062718091533e-05</v>
+        <v>0.004304228350520134</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0004436842864379287</v>
+        <v>0.0294248703867197</v>
       </c>
       <c r="DW5" t="n">
-        <v>5.370288999984041e-05</v>
+        <v>0.0003090851823799312</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0001857442402979359</v>
+        <v>0.002088324632495642</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.701702578633558e-05</v>
+        <v>0.01159494370222092</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.375088221626356e-06</v>
+        <v>0.0003635543398559093</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0001129970405600034</v>
+        <v>0.005294651724398136</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0004321959859225899</v>
+        <v>0.004948890767991543</v>
       </c>
       <c r="EC5" t="n">
-        <v>7.914264278952032e-05</v>
+        <v>0.0037162268999964</v>
       </c>
       <c r="ED5" t="n">
-        <v>9.285073610953987e-05</v>
+        <v>0.03204875439405441</v>
       </c>
       <c r="EE5" t="n">
-        <v>7.508269482059404e-05</v>
+        <v>0.02017071098089218</v>
       </c>
       <c r="EF5" t="n">
-        <v>6.641018990194425e-05</v>
+        <v>0.009212099947035313</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0002738913462962955</v>
+        <v>0.01372598111629486</v>
       </c>
       <c r="EH5" t="n">
-        <v>3.849381027976051e-05</v>
+        <v>0.007988439872860909</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0001968011347344145</v>
+        <v>0.02392687648534775</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0003107090014964342</v>
+        <v>0.007228732574731112</v>
       </c>
       <c r="EK5" t="n">
-        <v>4.102178718312643e-05</v>
+        <v>0.00610709935426712</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0002746601821854711</v>
+        <v>0.002385066822171211</v>
       </c>
       <c r="EM5" t="n">
-        <v>4.033079676446505e-05</v>
+        <v>0.004847059026360512</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0001263587910216302</v>
+        <v>0.00219927285797894</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001251343201147392</v>
+        <v>0.003116657957434654</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.000235119805438444</v>
+        <v>0.02260368689894676</v>
       </c>
       <c r="EQ5" t="n">
-        <v>8.295826410176232e-05</v>
+        <v>0.007022116333246231</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.351311897858977e-05</v>
+        <v>0.01227138563990593</v>
       </c>
       <c r="ES5" t="n">
-        <v>1.1624870239757e-05</v>
+        <v>0.001675195293501019</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.000175195891642943</v>
+        <v>0.008606645278632641</v>
       </c>
       <c r="EU5" t="n">
-        <v>6.971429684199393e-05</v>
+        <v>0.008507242426276207</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.00020979082910344</v>
+        <v>0.002680038101971149</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001781574101187289</v>
+        <v>0.008341092616319656</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0001156743674073368</v>
+        <v>0.0004304568283259869</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0002681650221347809</v>
+        <v>0.01709340885281563</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1.747580427036155e-05</v>
+        <v>0.001459592022001743</v>
       </c>
       <c r="FA5" t="n">
-        <v>7.792017277097329e-05</v>
+        <v>0.02548018284142017</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0001685984170762822</v>
+        <v>0.0009294406627304852</v>
       </c>
       <c r="FC5" t="n">
-        <v>9.623816004022956e-05</v>
+        <v>0.0009655187604948878</v>
       </c>
       <c r="FD5" t="n">
-        <v>3.489554728730582e-06</v>
+        <v>0.0005444049602374434</v>
       </c>
       <c r="FE5" t="n">
-        <v>4.827892189496197e-05</v>
+        <v>0.0003723539994098246</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0001015256202663295</v>
+        <v>0.002210740465670824</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0001195014920085669</v>
+        <v>0.006813189946115017</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0002656157885212451</v>
+        <v>0.006372608710080385</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0001615963119547814</v>
+        <v>0.007338596507906914</v>
       </c>
       <c r="FJ5" t="n">
-        <v>7.432666461681947e-05</v>
+        <v>0.0173194408416748</v>
       </c>
       <c r="FK5" t="n">
-        <v>8.761427307035774e-05</v>
+        <v>0.006821601651608944</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0002759471535682678</v>
+        <v>0.005255336407572031</v>
       </c>
       <c r="FM5" t="n">
-        <v>6.415329698938876e-05</v>
+        <v>0.001863498706370592</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001200759725179523</v>
+        <v>0.01003912556916475</v>
       </c>
       <c r="FO5" t="n">
-        <v>5.428133590612561e-06</v>
+        <v>0.00604540528729558</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0001678037078818306</v>
+        <v>0.0115779796615243</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001113203688873909</v>
+        <v>0.02260567434132099</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0003685253323055804</v>
+        <v>0.001783180981874466</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0001557865762151778</v>
+        <v>0.005255855619907379</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0004351922543719411</v>
+        <v>0.01865286566317081</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.000244800845393911</v>
+        <v>0.01848183572292328</v>
       </c>
       <c r="FV5" t="n">
-        <v>1.214949588757008e-05</v>
+        <v>0.006557569839060307</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0003319463576190174</v>
+        <v>0.004950223490595818</v>
       </c>
       <c r="FX5" t="n">
-        <v>4.789784725289792e-06</v>
+        <v>0.02475416287779808</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0001515939220553264</v>
+        <v>0.006023333873599768</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0001373176492052153</v>
+        <v>0.004329667892307043</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0002680514007806778</v>
+        <v>0.00714785885065794</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0001716300321277231</v>
+        <v>0.02510798536241055</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0004977715434506536</v>
+        <v>0.0003271194873377681</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0002751218271441758</v>
+        <v>0.004412590526044369</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0001604292192496359</v>
+        <v>0.01144691370427608</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0003044873010367155</v>
+        <v>0.000851978431455791</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0003427399205975235</v>
+        <v>0.0003975214203819633</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4.447089668246917e-05</v>
+        <v>5.159885648094165e-13</v>
       </c>
       <c r="B6" t="n">
-        <v>5.210983727010898e-05</v>
+        <v>1.358993646782825e-12</v>
       </c>
       <c r="C6" t="n">
-        <v>1.893171247502323e-05</v>
+        <v>4.536833148743868e-13</v>
       </c>
       <c r="D6" t="n">
-        <v>4.795168933924288e-05</v>
+        <v>7.159927490306417e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001397155574522913</v>
+        <v>9.53364232177123e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001334482803940773</v>
+        <v>2.128623449379474e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>5.94888006162364e-05</v>
+        <v>1.777905622203646e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>5.324052108335309e-05</v>
+        <v>3.723016686607572e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001405593211529776</v>
+        <v>9.798962991936291e-14</v>
       </c>
       <c r="J6" t="n">
-        <v>6.219393253559247e-05</v>
+        <v>8.542425664406772e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001120076994993724</v>
+        <v>3.725974335924004e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>2.310299896635115e-05</v>
+        <v>1.026823049331271e-12</v>
       </c>
       <c r="M6" t="n">
-        <v>1.025950041366741e-05</v>
+        <v>5.025223401462775e-13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001728389033814892</v>
+        <v>1.904119440246377e-12</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001203066422021948</v>
+        <v>2.466721488528223e-12</v>
       </c>
       <c r="P6" t="n">
-        <v>4.253444785717875e-06</v>
+        <v>2.807846403302117e-12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.192822310258634e-06</v>
+        <v>3.535852600294875e-12</v>
       </c>
       <c r="R6" t="n">
-        <v>5.002553371014073e-05</v>
+        <v>4.144963723379941e-13</v>
       </c>
       <c r="S6" t="n">
-        <v>3.444507092353888e-05</v>
+        <v>6.903946815281503e-13</v>
       </c>
       <c r="T6" t="n">
-        <v>3.647675839602016e-05</v>
+        <v>7.50639730495023e-13</v>
       </c>
       <c r="U6" t="n">
-        <v>5.267698725219816e-06</v>
+        <v>6.374114018721511e-14</v>
       </c>
       <c r="V6" t="n">
-        <v>5.19429704581853e-06</v>
+        <v>8.732558404687951e-13</v>
       </c>
       <c r="W6" t="n">
-        <v>4.778707807417959e-05</v>
+        <v>2.074869139348512e-12</v>
       </c>
       <c r="X6" t="n">
-        <v>4.58174072264228e-05</v>
+        <v>1.435797010798656e-13</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.383212085987907e-05</v>
+        <v>8.17757862293933e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.534408147563227e-05</v>
+        <v>2.388714226420063e-12</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.683285053237341e-05</v>
+        <v>6.763867081444747e-14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.838268417486688e-06</v>
+        <v>4.812826569569606e-13</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.163801587419584e-05</v>
+        <v>7.237887589620073e-13</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.137123611755669e-05</v>
+        <v>9.565587796682429e-14</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.295086935395375e-05</v>
+        <v>1.726082926763184e-13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0001472679723519832</v>
+        <v>9.087680694769285e-13</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0001252393703907728</v>
+        <v>1.557696463136415e-12</v>
       </c>
       <c r="AH6" t="n">
-        <v>9.537221922073513e-05</v>
+        <v>2.798323909831285e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.409805817180313e-05</v>
+        <v>1.074469289583102e-12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.693995187059045e-05</v>
+        <v>1.278116609944313e-13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.034304998232983e-05</v>
+        <v>1.135014120450667e-13</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.631171057350002e-05</v>
+        <v>3.147336449620119e-13</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.155231166194426e-05</v>
+        <v>1.188723327671254e-13</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.856268348405138e-05</v>
+        <v>5.424502535524012e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>5.573408270720392e-05</v>
+        <v>7.175809967931157e-13</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.351208175037755e-05</v>
+        <v>3.147304194605488e-13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.401923044701107e-05</v>
+        <v>6.016847176743001e-13</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.172891931375489e-05</v>
+        <v>5.293141684507841e-13</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.507111301179975e-05</v>
+        <v>3.989326501519647e-13</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.004690941248555e-05</v>
+        <v>1.579637841971765e-13</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.96885079680942e-05</v>
+        <v>2.046806951358504e-12</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.898073398682754e-05</v>
+        <v>1.111085724293803e-12</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.101429269416258e-05</v>
+        <v>6.918826405896694e-13</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0001048875710694119</v>
+        <v>1.180817813320467e-12</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.791688818135299e-05</v>
+        <v>2.532600214613656e-12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0001413749996572733</v>
+        <v>4.582042210932169e-13</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.341562013607472e-05</v>
+        <v>1.318150233062254e-12</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.069853432360105e-05</v>
+        <v>1.077962317932307e-13</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.255495827645063e-05</v>
+        <v>8.195894592340214e-13</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.844928768463433e-05</v>
+        <v>1.76017056832678e-12</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.344152203993872e-06</v>
+        <v>2.66153364538585e-13</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.010577761917375e-05</v>
+        <v>1.205639104176481e-12</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0001448227558284998</v>
+        <v>8.96261092685896e-13</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0001303951139561832</v>
+        <v>1.172658324610776e-12</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.385932359378785e-05</v>
+        <v>1.386595374110178e-13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>4.431817069416866e-05</v>
+        <v>3.120825863359156e-12</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.911595119163394e-05</v>
+        <v>4.319885378231691e-13</v>
       </c>
       <c r="BL6" t="n">
-        <v>6.492919055745006e-07</v>
+        <v>6.900358106090576e-13</v>
       </c>
       <c r="BM6" t="n">
-        <v>6.919360748725012e-05</v>
+        <v>2.900290142597572e-13</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.141652607358992e-05</v>
+        <v>2.884300328957756e-13</v>
       </c>
       <c r="BO6" t="n">
-        <v>6.489372754003853e-05</v>
+        <v>2.656840676282246e-13</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.230736597790383e-05</v>
+        <v>7.596306396406849e-13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.341634874232113e-05</v>
+        <v>4.269692780757561e-13</v>
       </c>
       <c r="BR6" t="n">
-        <v>7.711032230872661e-05</v>
+        <v>1.782568775747506e-13</v>
       </c>
       <c r="BS6" t="n">
-        <v>3.2704915611248e-06</v>
+        <v>8.834241931737763e-15</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.141643123351969e-05</v>
+        <v>4.763071447672074e-13</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.635222179174889e-05</v>
+        <v>5.129455345719014e-13</v>
       </c>
       <c r="BV6" t="n">
-        <v>4.3160425775568e-06</v>
+        <v>1.087952969901218e-13</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.709283191710711e-05</v>
+        <v>2.939272089608203e-14</v>
       </c>
       <c r="BX6" t="n">
-        <v>2.418453186692204e-05</v>
+        <v>1.967155821916422e-12</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.546970689669251e-05</v>
+        <v>1.275071736563105e-12</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.709917680476792e-06</v>
+        <v>4.553867049075788e-13</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.471944935678039e-05</v>
+        <v>7.163581251627693e-15</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.317377170082182e-05</v>
+        <v>8.396293642992658e-13</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.829385605058633e-05</v>
+        <v>1.20160961259233e-13</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.19730315823108e-06</v>
+        <v>2.17113721207203e-13</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.414613689121325e-05</v>
+        <v>1.590023279056732e-13</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.694336060609203e-05</v>
+        <v>1.119404319672307e-13</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.85544683720218e-05</v>
+        <v>1.674705838415613e-13</v>
       </c>
       <c r="CH6" t="n">
-        <v>6.062414286134299e-06</v>
+        <v>4.158956165567496e-14</v>
       </c>
       <c r="CI6" t="n">
-        <v>7.038802323222626e-06</v>
+        <v>4.369679531407433e-13</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.387675365549512e-05</v>
+        <v>2.833157428279443e-13</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.539363802294247e-05</v>
+        <v>2.010604681877692e-13</v>
       </c>
       <c r="CL6" t="n">
-        <v>3.337772068334743e-05</v>
+        <v>6.211891894966626e-13</v>
       </c>
       <c r="CM6" t="n">
-        <v>7.498436389141716e-06</v>
+        <v>6.253295407529502e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>3.97003605030477e-05</v>
+        <v>9.761753037851317e-13</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.914213135023601e-05</v>
+        <v>6.526717100802104e-13</v>
       </c>
       <c r="CP6" t="n">
-        <v>4.637351958081126e-05</v>
+        <v>7.832766553417247e-13</v>
       </c>
       <c r="CQ6" t="n">
-        <v>8.027442527236417e-05</v>
+        <v>6.355328589779941e-13</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.190225430036662e-05</v>
+        <v>7.900658751357204e-13</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.554365735501051e-05</v>
+        <v>1.220058234129018e-12</v>
       </c>
       <c r="CT6" t="n">
-        <v>1.813372364267707e-05</v>
+        <v>9.871595728350169e-13</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0001472574658691883</v>
+        <v>1.29539532312678e-12</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.149944066331955e-06</v>
+        <v>1.446262001218029e-13</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.121146644640248e-05</v>
+        <v>1.033687566966146e-13</v>
       </c>
       <c r="CX6" t="n">
-        <v>2.608338490972528e-06</v>
+        <v>1.530229935819971e-13</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.435041824355721e-05</v>
+        <v>1.634886751802553e-13</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.286052611249033e-05</v>
+        <v>4.538645392675178e-13</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.006275851977989e-05</v>
+        <v>6.115621247262948e-13</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.218786565004848e-06</v>
+        <v>4.576228176782215e-13</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.033574244502233e-05</v>
+        <v>1.471796588683322e-13</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.133791324216872e-05</v>
+        <v>5.863244460259376e-13</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.220552960352506e-05</v>
+        <v>1.579480903707298e-12</v>
       </c>
       <c r="DF6" t="n">
-        <v>7.239637488964945e-05</v>
+        <v>2.258413941969017e-12</v>
       </c>
       <c r="DG6" t="n">
-        <v>8.835035259835422e-06</v>
+        <v>1.018431432936451e-12</v>
       </c>
       <c r="DH6" t="n">
-        <v>7.766031194478273e-05</v>
+        <v>1.236844719525176e-12</v>
       </c>
       <c r="DI6" t="n">
-        <v>1.131684075517114e-05</v>
+        <v>6.777057756125748e-14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0001364810887025669</v>
+        <v>2.662954926013761e-12</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.165717059047893e-05</v>
+        <v>3.48990882850439e-13</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.21301870624302e-05</v>
+        <v>3.15067796071572e-14</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.00011473371705506</v>
+        <v>8.733354209082556e-14</v>
       </c>
       <c r="DN6" t="n">
-        <v>3.144010042888112e-05</v>
+        <v>1.048336547779249e-12</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.079252953990363e-05</v>
+        <v>3.199990186025792e-14</v>
       </c>
       <c r="DP6" t="n">
-        <v>4.570818418869749e-06</v>
+        <v>1.005312166521034e-13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.018874172586948e-06</v>
+        <v>1.482258651756829e-12</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.819941624300554e-05</v>
+        <v>1.397106280491556e-12</v>
       </c>
       <c r="DS6" t="n">
-        <v>5.531570786843076e-05</v>
+        <v>7.565247256771657e-13</v>
       </c>
       <c r="DT6" t="n">
-        <v>8.023284317459911e-05</v>
+        <v>8.191944301724763e-13</v>
       </c>
       <c r="DU6" t="n">
-        <v>1.05841672848328e-05</v>
+        <v>7.165650451473882e-13</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0001104967086575925</v>
+        <v>7.221728369390806e-14</v>
       </c>
       <c r="DW6" t="n">
-        <v>3.1487230444327e-05</v>
+        <v>4.96335774129858e-13</v>
       </c>
       <c r="DX6" t="n">
-        <v>2.298670369782485e-05</v>
+        <v>7.6839327001893e-13</v>
       </c>
       <c r="DY6" t="n">
-        <v>3.275944436609279e-06</v>
+        <v>8.913073729598098e-13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.138701817486435e-05</v>
+        <v>9.03547744436628e-13</v>
       </c>
       <c r="EA6" t="n">
-        <v>3.805633241427131e-05</v>
+        <v>1.547660437306586e-12</v>
       </c>
       <c r="EB6" t="n">
-        <v>2.103737097058911e-05</v>
+        <v>9.682655068357637e-13</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.551779132569209e-05</v>
+        <v>6.902899475982882e-13</v>
       </c>
       <c r="ED6" t="n">
-        <v>3.19603095704224e-05</v>
+        <v>4.425151109259395e-13</v>
       </c>
       <c r="EE6" t="n">
-        <v>2.767737896647304e-06</v>
+        <v>2.215653875647927e-13</v>
       </c>
       <c r="EF6" t="n">
-        <v>1.16092751341057e-05</v>
+        <v>3.707488959933669e-14</v>
       </c>
       <c r="EG6" t="n">
-        <v>1.921462353493553e-05</v>
+        <v>1.901758102124812e-13</v>
       </c>
       <c r="EH6" t="n">
-        <v>1.319343573413789e-05</v>
+        <v>6.344937596158839e-13</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0001250394270755351</v>
+        <v>8.435120549092623e-13</v>
       </c>
       <c r="EJ6" t="n">
-        <v>2.656545620993711e-05</v>
+        <v>9.535360782214619e-13</v>
       </c>
       <c r="EK6" t="n">
-        <v>8.683668420417234e-05</v>
+        <v>5.51943419354467e-13</v>
       </c>
       <c r="EL6" t="n">
-        <v>7.067398109938949e-05</v>
+        <v>5.177274760162845e-14</v>
       </c>
       <c r="EM6" t="n">
-        <v>2.012908771575894e-05</v>
+        <v>1.024572408251517e-13</v>
       </c>
       <c r="EN6" t="n">
-        <v>2.342241714359261e-05</v>
+        <v>7.763642701809348e-13</v>
       </c>
       <c r="EO6" t="n">
-        <v>3.320008545415476e-05</v>
+        <v>2.241041553718848e-13</v>
       </c>
       <c r="EP6" t="n">
-        <v>1.466584126319503e-05</v>
+        <v>8.656774299134473e-13</v>
       </c>
       <c r="EQ6" t="n">
-        <v>1.964676630450413e-05</v>
+        <v>9.74711779930075e-14</v>
       </c>
       <c r="ER6" t="n">
-        <v>7.052171895338688e-06</v>
+        <v>3.727169668819169e-13</v>
       </c>
       <c r="ES6" t="n">
-        <v>1.449663250241429e-05</v>
+        <v>9.749196892491763e-13</v>
       </c>
       <c r="ET6" t="n">
-        <v>5.466331640491262e-05</v>
+        <v>2.001608920927309e-13</v>
       </c>
       <c r="EU6" t="n">
-        <v>4.391351831145585e-05</v>
+        <v>3.597001711243275e-13</v>
       </c>
       <c r="EV6" t="n">
-        <v>6.552630111400504e-06</v>
+        <v>5.715366331246474e-14</v>
       </c>
       <c r="EW6" t="n">
-        <v>2.325874265807215e-05</v>
+        <v>1.247249374093651e-13</v>
       </c>
       <c r="EX6" t="n">
-        <v>3.552627049430157e-06</v>
+        <v>1.793687540076888e-13</v>
       </c>
       <c r="EY6" t="n">
-        <v>1.567858998896554e-05</v>
+        <v>5.386109039242498e-14</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1.799697020032909e-05</v>
+        <v>7.562597466662102e-14</v>
       </c>
       <c r="FA6" t="n">
-        <v>3.903486503986642e-05</v>
+        <v>2.030248798939871e-13</v>
       </c>
       <c r="FB6" t="n">
-        <v>9.846011380432174e-06</v>
+        <v>3.413395325939372e-13</v>
       </c>
       <c r="FC6" t="n">
-        <v>4.336211986810667e-06</v>
+        <v>5.781160055881585e-13</v>
       </c>
       <c r="FD6" t="n">
-        <v>9.380361007060856e-06</v>
+        <v>3.158238644565547e-13</v>
       </c>
       <c r="FE6" t="n">
-        <v>5.166788923816057e-06</v>
+        <v>2.69218973286342e-13</v>
       </c>
       <c r="FF6" t="n">
-        <v>1.248609260073863e-05</v>
+        <v>5.269074022581921e-13</v>
       </c>
       <c r="FG6" t="n">
-        <v>6.480513548012823e-06</v>
+        <v>1.395087170785736e-12</v>
       </c>
       <c r="FH6" t="n">
-        <v>2.942161336250138e-05</v>
+        <v>5.332033642738154e-13</v>
       </c>
       <c r="FI6" t="n">
-        <v>2.898819730035029e-05</v>
+        <v>5.325696481039977e-13</v>
       </c>
       <c r="FJ6" t="n">
-        <v>7.110673323040828e-05</v>
+        <v>4.266885781332996e-14</v>
       </c>
       <c r="FK6" t="n">
-        <v>4.873510988545604e-05</v>
+        <v>7.50882442703861e-14</v>
       </c>
       <c r="FL6" t="n">
-        <v>3.446820119279437e-05</v>
+        <v>7.354716878918421e-13</v>
       </c>
       <c r="FM6" t="n">
-        <v>2.44035036303103e-05</v>
+        <v>4.401393935730621e-14</v>
       </c>
       <c r="FN6" t="n">
-        <v>1.535428600618616e-05</v>
+        <v>1.761737023625587e-12</v>
       </c>
       <c r="FO6" t="n">
-        <v>6.641005893470719e-05</v>
+        <v>1.045241150576803e-12</v>
       </c>
       <c r="FP6" t="n">
-        <v>5.208969741943292e-05</v>
+        <v>6.78211176455279e-13</v>
       </c>
       <c r="FQ6" t="n">
-        <v>2.673165363376029e-05</v>
+        <v>1.136857860455087e-12</v>
       </c>
       <c r="FR6" t="n">
-        <v>6.574027065653354e-05</v>
+        <v>1.97980087185412e-12</v>
       </c>
       <c r="FS6" t="n">
-        <v>4.808016456081532e-06</v>
+        <v>2.289512438143071e-13</v>
       </c>
       <c r="FT6" t="n">
-        <v>9.426561882719398e-05</v>
+        <v>3.65236324257473e-13</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.000143939585541375</v>
+        <v>1.658400386418332e-13</v>
       </c>
       <c r="FV6" t="n">
-        <v>2.63444526353851e-05</v>
+        <v>2.237745145433623e-12</v>
       </c>
       <c r="FW6" t="n">
-        <v>4.5982076699147e-05</v>
+        <v>1.29059425906658e-12</v>
       </c>
       <c r="FX6" t="n">
-        <v>2.412903450021986e-05</v>
+        <v>7.901971720188083e-13</v>
       </c>
       <c r="FY6" t="n">
-        <v>2.769147613435052e-05</v>
+        <v>1.562653272838693e-13</v>
       </c>
       <c r="FZ6" t="n">
-        <v>4.296127735869959e-05</v>
+        <v>2.047028995963429e-13</v>
       </c>
       <c r="GA6" t="n">
-        <v>4.58989707112778e-05</v>
+        <v>5.38414148334998e-13</v>
       </c>
       <c r="GB6" t="n">
-        <v>2.684155151655432e-05</v>
+        <v>3.032461976838763e-13</v>
       </c>
       <c r="GC6" t="n">
-        <v>5.20871180924587e-05</v>
+        <v>1.188925694006748e-12</v>
       </c>
       <c r="GD6" t="n">
-        <v>3.013929381268099e-05</v>
+        <v>7.081793376544077e-13</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0001125711278291419</v>
+        <v>9.149384944335051e-14</v>
       </c>
       <c r="GF6" t="n">
-        <v>7.575310883112252e-05</v>
+        <v>1.228773159611674e-12</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.000158237962750718</v>
+        <v>2.581368278853358e-13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.202906441122309e-09</v>
+        <v>4.103133144745993e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>9.09483599542682e-11</v>
+        <v>4.144193066864145e-18</v>
       </c>
       <c r="C7" t="n">
-        <v>1.081916001233196e-09</v>
+        <v>2.766345019470317e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>2.46521414393186e-10</v>
+        <v>2.492198570926726e-16</v>
       </c>
       <c r="E7" t="n">
-        <v>5.686286996819945e-10</v>
+        <v>1.290225334501678e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>8.197897916062402e-10</v>
+        <v>5.554090326353013e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.84979698225618e-09</v>
+        <v>8.827380329590293e-18</v>
       </c>
       <c r="H7" t="n">
-        <v>1.203196153820585e-10</v>
+        <v>6.935754588046467e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>4.152841404092555e-10</v>
+        <v>5.125223251477176e-16</v>
       </c>
       <c r="J7" t="n">
-        <v>3.792893221721272e-10</v>
+        <v>2.347992038837294e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>1.264360061092873e-09</v>
+        <v>4.814720560650655e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>1.327046028620771e-09</v>
+        <v>2.610772066234896e-16</v>
       </c>
       <c r="M7" t="n">
-        <v>9.405657364069953e-10</v>
+        <v>5.127984578885225e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>3.994077957258924e-09</v>
+        <v>6.724879780127099e-17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.309313018589165e-10</v>
+        <v>5.092278963784904e-16</v>
       </c>
       <c r="P7" t="n">
-        <v>5.081994269851009e-10</v>
+        <v>1.10151565827628e-16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.739637989217613e-09</v>
+        <v>2.367028277146222e-16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.541051730669096e-09</v>
+        <v>3.700229019366929e-16</v>
       </c>
       <c r="S7" t="n">
-        <v>1.297509599762492e-10</v>
+        <v>1.139796915280744e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>9.878875495417105e-11</v>
+        <v>2.745911673106787e-16</v>
       </c>
       <c r="U7" t="n">
-        <v>2.307887075891912e-10</v>
+        <v>1.207591976541101e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>3.298016026942463e-10</v>
+        <v>3.045491079985076e-16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.90960755489067e-10</v>
+        <v>5.185163537989627e-16</v>
       </c>
       <c r="X7" t="n">
-        <v>1.504601110369208e-09</v>
+        <v>2.330110081442347e-16</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.326850237632243e-10</v>
+        <v>1.010508188492012e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.342815634357123e-10</v>
+        <v>1.372712049883262e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.061425045079112e-10</v>
+        <v>1.159709071683917e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.999459593679205e-12</v>
+        <v>1.517240222882079e-16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.751820216666644e-10</v>
+        <v>1.417258174323855e-16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.223608769862494e-09</v>
+        <v>1.386897204771811e-16</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.848230235523829e-09</v>
+        <v>3.50403977751948e-16</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.075525638138402e-10</v>
+        <v>1.822702405927947e-18</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.931380138626594e-10</v>
+        <v>2.113850658607504e-16</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.811278680489806e-10</v>
+        <v>8.949906954133077e-17</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.01487193385708e-10</v>
+        <v>3.074526840021361e-16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.390935724023052e-10</v>
+        <v>8.853925548063854e-17</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.605807957247521e-10</v>
+        <v>1.434529043769473e-16</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.514619263343064e-10</v>
+        <v>1.586694409927869e-16</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.748249878197328e-10</v>
+        <v>7.645482832806355e-17</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.643568473130301e-10</v>
+        <v>3.518821031844659e-16</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.304044316974284e-09</v>
+        <v>1.724007450402856e-16</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.241369005481999e-10</v>
+        <v>3.567142937996537e-17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.515783580405497e-10</v>
+        <v>1.782323418890049e-17</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.219419423914019e-10</v>
+        <v>8.901666442553475e-17</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.027294083133512e-10</v>
+        <v>8.106636024304668e-17</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.079615451540008e-10</v>
+        <v>1.03296792883295e-17</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.977824126697669e-09</v>
+        <v>6.977262908231072e-16</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.298723239009149e-10</v>
+        <v>8.880739434800373e-17</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.41173242172033e-11</v>
+        <v>1.724405688236964e-16</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.346160098478435e-10</v>
+        <v>1.686325336859676e-16</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.7141238428664e-09</v>
+        <v>2.205252759718409e-17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.038858414379121e-10</v>
+        <v>4.922676564139441e-17</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.114656227902856e-10</v>
+        <v>1.508022386833584e-16</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.257182913327881e-09</v>
+        <v>1.646683268485889e-16</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.259171597162606e-10</v>
+        <v>1.695811708822231e-16</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.858524693673871e-11</v>
+        <v>2.066970958397224e-16</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.672840613397568e-10</v>
+        <v>2.4712699088124e-17</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.7428558009629e-10</v>
+        <v>2.226930086461545e-16</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.651680570091685e-09</v>
+        <v>4.244590624787666e-17</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.634310016437553e-11</v>
+        <v>2.838061446229766e-16</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.407401500370554e-10</v>
+        <v>1.491598020939629e-16</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2.861550441046745e-10</v>
+        <v>2.329350663465575e-16</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.34769351234354e-09</v>
+        <v>1.449477190055041e-16</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.916839547673078e-10</v>
+        <v>2.128114164043674e-16</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.712400887754484e-09</v>
+        <v>2.019326281556456e-16</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.430117274603404e-10</v>
+        <v>2.11615895573767e-17</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.902132033635098e-10</v>
+        <v>5.147898985219664e-17</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.902349554607554e-09</v>
+        <v>2.935128245611557e-16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.31365429224229e-10</v>
+        <v>2.223464662916091e-16</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.045097008933737e-09</v>
+        <v>3.188985872788243e-16</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.941852234565999e-09</v>
+        <v>4.608986845674426e-17</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.733353012464363e-11</v>
+        <v>3.916006692213022e-17</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.065466214202672e-10</v>
+        <v>2.921069550095055e-17</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.021074998116774e-10</v>
+        <v>9.139444472715518e-17</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.902972306983997e-10</v>
+        <v>1.80636724319125e-16</v>
       </c>
       <c r="BX7" t="n">
-        <v>4.728686331390008e-10</v>
+        <v>3.318366979107785e-16</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.332221333250061e-09</v>
+        <v>2.780566702654716e-16</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.770874333954623e-10</v>
+        <v>3.013893574678938e-16</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.950457514560583e-10</v>
+        <v>5.620997988252223e-17</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.244992247657507e-10</v>
+        <v>2.168180410635579e-16</v>
       </c>
       <c r="CC7" t="n">
-        <v>8.131766926489092e-10</v>
+        <v>2.994026152203293e-16</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.237207419846342e-10</v>
+        <v>6.925533282653272e-17</v>
       </c>
       <c r="CE7" t="n">
-        <v>3.314038488078097e-10</v>
+        <v>1.107188446373557e-17</v>
       </c>
       <c r="CF7" t="n">
-        <v>4.310934942353128e-11</v>
+        <v>4.476110868179623e-17</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.867689974372922e-10</v>
+        <v>1.11258995231714e-16</v>
       </c>
       <c r="CH7" t="n">
-        <v>9.299089276382233e-12</v>
+        <v>1.347545791121663e-17</v>
       </c>
       <c r="CI7" t="n">
-        <v>3.215642196963131e-10</v>
+        <v>8.875548711020481e-17</v>
       </c>
       <c r="CJ7" t="n">
-        <v>4.433011735471837e-10</v>
+        <v>5.531050699315451e-17</v>
       </c>
       <c r="CK7" t="n">
-        <v>3.287913830085643e-10</v>
+        <v>5.071839397023168e-17</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.823000444518442e-10</v>
+        <v>1.318126467435337e-16</v>
       </c>
       <c r="CM7" t="n">
-        <v>8.491314873459999e-10</v>
+        <v>5.259917769005065e-17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.557160511644895e-09</v>
+        <v>3.309793682192591e-16</v>
       </c>
       <c r="CO7" t="n">
-        <v>4.13069051186099e-10</v>
+        <v>1.504071110483541e-16</v>
       </c>
       <c r="CP7" t="n">
-        <v>3.75848657752087e-10</v>
+        <v>2.107661494741035e-17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.576452828861875e-09</v>
+        <v>1.628988750217747e-16</v>
       </c>
       <c r="CR7" t="n">
-        <v>3.781835955507518e-10</v>
+        <v>1.762199107203368e-17</v>
       </c>
       <c r="CS7" t="n">
-        <v>5.828248439421202e-10</v>
+        <v>7.559926549433261e-17</v>
       </c>
       <c r="CT7" t="n">
-        <v>8.736363854566775e-10</v>
+        <v>1.190432147820912e-16</v>
       </c>
       <c r="CU7" t="n">
-        <v>6.813163366814479e-10</v>
+        <v>1.555346514643376e-16</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.671509194418498e-11</v>
+        <v>9.335758916620483e-17</v>
       </c>
       <c r="CW7" t="n">
-        <v>3.406485371559853e-10</v>
+        <v>2.014552556066963e-17</v>
       </c>
       <c r="CX7" t="n">
-        <v>6.457337442533628e-11</v>
+        <v>2.558233060971324e-17</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.321699776874908e-10</v>
+        <v>1.310646901813285e-16</v>
       </c>
       <c r="CZ7" t="n">
-        <v>5.297910721235866e-11</v>
+        <v>3.081584278833215e-17</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.916124841600976e-10</v>
+        <v>8.846539156066001e-17</v>
       </c>
       <c r="DB7" t="n">
-        <v>4.881288151459273e-10</v>
+        <v>2.847417057481088e-17</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.576002466891936e-10</v>
+        <v>2.2985198553256e-17</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.874541825212631e-11</v>
+        <v>1.181822587307665e-16</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.018377687207362e-09</v>
+        <v>9.290429419052577e-17</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.067236826164276e-09</v>
+        <v>1.151523821737684e-16</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.152555828554114e-11</v>
+        <v>1.037029981210626e-16</v>
       </c>
       <c r="DH7" t="n">
-        <v>2.340047711157922e-09</v>
+        <v>8.405508291020898e-17</v>
       </c>
       <c r="DI7" t="n">
-        <v>2.561950429580406e-09</v>
+        <v>2.450024601959588e-17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.210910816062949e-09</v>
+        <v>2.163295677507881e-16</v>
       </c>
       <c r="DK7" t="n">
-        <v>1.960489104391172e-09</v>
+        <v>9.004711971053901e-17</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.916125702550175e-09</v>
+        <v>1.306648376906653e-16</v>
       </c>
       <c r="DM7" t="n">
-        <v>5.134639380344197e-10</v>
+        <v>1.113295239594627e-16</v>
       </c>
       <c r="DN7" t="n">
-        <v>3.484596777791893e-10</v>
+        <v>6.496616973987376e-17</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.890502476786793e-10</v>
+        <v>4.389447155402442e-17</v>
       </c>
       <c r="DP7" t="n">
-        <v>4.319470336966447e-10</v>
+        <v>2.608005676481498e-17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>3.752285426816826e-10</v>
+        <v>2.656116386879378e-16</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.74265651592998e-10</v>
+        <v>8.801703319887667e-17</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.101482516308039e-10</v>
+        <v>2.183634262060437e-16</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.252971171261663e-09</v>
+        <v>1.702634691561262e-16</v>
       </c>
       <c r="DU7" t="n">
-        <v>8.93022378267716e-10</v>
+        <v>5.932708098075275e-17</v>
       </c>
       <c r="DV7" t="n">
-        <v>1.291228651778553e-10</v>
+        <v>4.351608274589571e-17</v>
       </c>
       <c r="DW7" t="n">
-        <v>7.264884527291571e-11</v>
+        <v>1.289332508835713e-16</v>
       </c>
       <c r="DX7" t="n">
-        <v>3.535306769553159e-10</v>
+        <v>7.828658339861528e-17</v>
       </c>
       <c r="DY7" t="n">
-        <v>3.633170153616305e-10</v>
+        <v>4.81744562446065e-17</v>
       </c>
       <c r="DZ7" t="n">
-        <v>8.696750541936638e-10</v>
+        <v>9.81366681686218e-17</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.534366106392682e-10</v>
+        <v>1.795461032250861e-17</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.910106045028726e-10</v>
+        <v>1.268564518283568e-17</v>
       </c>
       <c r="EC7" t="n">
-        <v>5.470580100030986e-10</v>
+        <v>1.813234562811114e-16</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.225005430427473e-09</v>
+        <v>6.534691766710946e-17</v>
       </c>
       <c r="EE7" t="n">
-        <v>4.439031364711354e-10</v>
+        <v>3.515850129956614e-17</v>
       </c>
       <c r="EF7" t="n">
-        <v>2.70640038158021e-10</v>
+        <v>4.417844596703633e-17</v>
       </c>
       <c r="EG7" t="n">
-        <v>8.732402578814913e-10</v>
+        <v>8.867851960856797e-17</v>
       </c>
       <c r="EH7" t="n">
-        <v>3.198908915535981e-10</v>
+        <v>7.728899034498653e-17</v>
       </c>
       <c r="EI7" t="n">
-        <v>1.247080660959909e-09</v>
+        <v>2.303295135914644e-16</v>
       </c>
       <c r="EJ7" t="n">
-        <v>8.566941600562927e-11</v>
+        <v>3.740447864238237e-17</v>
       </c>
       <c r="EK7" t="n">
-        <v>6.815485953381994e-10</v>
+        <v>7.48270692314572e-17</v>
       </c>
       <c r="EL7" t="n">
-        <v>1.360665052851928e-10</v>
+        <v>5.596811227141172e-17</v>
       </c>
       <c r="EM7" t="n">
-        <v>7.44089373450052e-11</v>
+        <v>7.317085512177903e-17</v>
       </c>
       <c r="EN7" t="n">
-        <v>2.056723402699134e-10</v>
+        <v>1.521382081645255e-16</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.690593776082494e-10</v>
+        <v>1.140213284913879e-16</v>
       </c>
       <c r="EP7" t="n">
-        <v>4.579224777145896e-10</v>
+        <v>2.467136718902044e-16</v>
       </c>
       <c r="EQ7" t="n">
-        <v>4.099448211447587e-12</v>
+        <v>2.307346070984888e-16</v>
       </c>
       <c r="ER7" t="n">
-        <v>8.910963078534451e-10</v>
+        <v>5.724649674705527e-17</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.409653505035635e-10</v>
+        <v>6.183891086372108e-17</v>
       </c>
       <c r="ET7" t="n">
-        <v>8.79680217558132e-11</v>
+        <v>1.928417411701204e-16</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.446969488672067e-10</v>
+        <v>1.429810937904368e-16</v>
       </c>
       <c r="EV7" t="n">
-        <v>4.201674563830693e-10</v>
+        <v>1.141822382815866e-16</v>
       </c>
       <c r="EW7" t="n">
-        <v>5.603962294209452e-10</v>
+        <v>1.064132388544804e-16</v>
       </c>
       <c r="EX7" t="n">
-        <v>5.748904130520316e-11</v>
+        <v>1.287371098167227e-16</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.778280300790414e-10</v>
+        <v>4.897126940251148e-17</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.207852845519497e-10</v>
+        <v>6.628138691383307e-17</v>
       </c>
       <c r="FA7" t="n">
-        <v>1.649331227149275e-10</v>
+        <v>1.106609304139484e-16</v>
       </c>
       <c r="FB7" t="n">
-        <v>5.712716411032659e-11</v>
+        <v>1.059561289218162e-17</v>
       </c>
       <c r="FC7" t="n">
-        <v>6.208353275916068e-10</v>
+        <v>1.033002604244228e-16</v>
       </c>
       <c r="FD7" t="n">
-        <v>5.327182583947376e-10</v>
+        <v>8.200031994651296e-17</v>
       </c>
       <c r="FE7" t="n">
-        <v>4.888566218497203e-10</v>
+        <v>3.983623082461066e-17</v>
       </c>
       <c r="FF7" t="n">
-        <v>7.8364419120458e-11</v>
+        <v>1.418397036591219e-16</v>
       </c>
       <c r="FG7" t="n">
-        <v>3.104303480938597e-10</v>
+        <v>3.027444513648231e-16</v>
       </c>
       <c r="FH7" t="n">
-        <v>3.766644496305815e-10</v>
+        <v>1.000553301430508e-16</v>
       </c>
       <c r="FI7" t="n">
-        <v>4.465247616103341e-13</v>
+        <v>1.546047416371504e-16</v>
       </c>
       <c r="FJ7" t="n">
-        <v>5.970277050515449e-10</v>
+        <v>9.113206303685336e-17</v>
       </c>
       <c r="FK7" t="n">
-        <v>3.212091148618867e-10</v>
+        <v>1.221397356266815e-17</v>
       </c>
       <c r="FL7" t="n">
-        <v>3.752292920822242e-11</v>
+        <v>2.000341626230527e-16</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.844303321174579e-10</v>
+        <v>2.532569749379642e-16</v>
       </c>
       <c r="FN7" t="n">
-        <v>4.531528208229219e-10</v>
+        <v>8.524847292355148e-18</v>
       </c>
       <c r="FO7" t="n">
-        <v>6.747065128820395e-10</v>
+        <v>1.009004705010636e-16</v>
       </c>
       <c r="FP7" t="n">
-        <v>5.972396466269458e-10</v>
+        <v>3.105438513338019e-17</v>
       </c>
       <c r="FQ7" t="n">
-        <v>1.796626847294647e-09</v>
+        <v>1.418011901298014e-16</v>
       </c>
       <c r="FR7" t="n">
-        <v>5.739345110278293e-10</v>
+        <v>4.383721080330105e-17</v>
       </c>
       <c r="FS7" t="n">
-        <v>5.004060499302909e-10</v>
+        <v>2.343931806256965e-16</v>
       </c>
       <c r="FT7" t="n">
-        <v>5.020663329524666e-10</v>
+        <v>2.899049141921056e-16</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.161460261300817e-09</v>
+        <v>5.102160860429157e-17</v>
       </c>
       <c r="FV7" t="n">
-        <v>3.649280322370885e-10</v>
+        <v>2.404483544678215e-16</v>
       </c>
       <c r="FW7" t="n">
-        <v>2.870719217895612e-10</v>
+        <v>1.725509610395252e-16</v>
       </c>
       <c r="FX7" t="n">
-        <v>5.061401853190262e-10</v>
+        <v>1.979944940511745e-16</v>
       </c>
       <c r="FY7" t="n">
-        <v>3.092898853696013e-11</v>
+        <v>7.352751554957719e-17</v>
       </c>
       <c r="FZ7" t="n">
-        <v>8.639248205710715e-10</v>
+        <v>8.564524168489112e-17</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.087013812295368e-09</v>
+        <v>5.308444154204366e-17</v>
       </c>
       <c r="GB7" t="n">
-        <v>5.191181373653819e-10</v>
+        <v>8.613060479855763e-17</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.934804316761074e-09</v>
+        <v>1.033121718252436e-16</v>
       </c>
       <c r="GD7" t="n">
-        <v>1.19883170057733e-09</v>
+        <v>2.324351051494406e-16</v>
       </c>
       <c r="GE7" t="n">
-        <v>6.408497066345831e-10</v>
+        <v>5.143375961630224e-18</v>
       </c>
       <c r="GF7" t="n">
-        <v>8.98372154445326e-10</v>
+        <v>1.104199429230096e-16</v>
       </c>
       <c r="GG7" t="n">
-        <v>3.692308403469013e-10</v>
+        <v>1.078882673227849e-16</v>
       </c>
     </row>
     <row r="8">
@@ -4982,4554 +4982,4554 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.000344688247423619</v>
+        <v>0.00181038910523057</v>
       </c>
       <c r="B9" t="n">
-        <v>0.007689959369599819</v>
+        <v>0.003797923214733601</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006043091416358948</v>
+        <v>0.0001921334769576788</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00575983477756381</v>
+        <v>0.004794349428266287</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002431112341582775</v>
+        <v>0.0001248954795300961</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002503614407032728</v>
+        <v>0.006963158957660198</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001586697180755436</v>
+        <v>0.004292312543839216</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001449698116630316</v>
+        <v>0.004254631698131561</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00177635985892266</v>
+        <v>0.0005509742768481374</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009974651038646698</v>
+        <v>0.001550265704281628</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005363583099097013</v>
+        <v>0.003004699246957898</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004360623715911061</v>
+        <v>0.001289851265028119</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005866115912795067</v>
+        <v>0.008227403275668621</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004994221031665802</v>
+        <v>0.002619798295199871</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003760610707104206</v>
+        <v>0.00839316938072443</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0005002751713618636</v>
+        <v>0.00511386152356863</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0005295996088534594</v>
+        <v>0.001423605834133923</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002647273242473602</v>
+        <v>0.001446792972274125</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003486441564746201</v>
+        <v>0.0008072190103121102</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001191523973830044</v>
+        <v>7.601332617923617e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.217921453644522e-05</v>
+        <v>0.001489729853346944</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001260245451703668</v>
+        <v>0.0001080509100575</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0008368251728825271</v>
+        <v>0.001384892966598272</v>
       </c>
       <c r="X9" t="n">
-        <v>0.000358867080649361</v>
+        <v>0.002651841146871448</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001064740470610559</v>
+        <v>0.0002198646543547511</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.706727875396609e-05</v>
+        <v>0.001522060018032789</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.000593985547311604</v>
+        <v>0.001219079247675836</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0006533308187499642</v>
+        <v>0.00146794633474201</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001626176293939352</v>
+        <v>0.00123787927441299</v>
       </c>
       <c r="AD9" t="n">
-        <v>7.884642400313169e-05</v>
+        <v>0.001547315856441855</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0008979274425655603</v>
+        <v>0.0009158931206911802</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002357295947149396</v>
+        <v>0.001560335978865623</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001146286493167281</v>
+        <v>0.003296921495348215</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0004827371740248054</v>
+        <v>0.0004225790034979582</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0002163086319342256</v>
+        <v>0.002512735780328512</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0001447177928639576</v>
+        <v>0.001430910313501954</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0004669971531257033</v>
+        <v>0.0009478520369157195</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0005745395319536328</v>
+        <v>0.001759022241458297</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0001250734785571694</v>
+        <v>0.002258532680571079</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.251547605032101e-05</v>
+        <v>0.001578515162691474</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001802708953619003</v>
+        <v>0.0001832321431720629</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001389157143421471</v>
+        <v>0.001935852458700538</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.000460945040686056</v>
+        <v>0.001361028756946325</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0004420126788318157</v>
+        <v>0.0005640472518280149</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0007439288892783225</v>
+        <v>0.001089084194973111</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0009840517304837704</v>
+        <v>0.0003163450455758721</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006122764199972153</v>
+        <v>0.001725392881780863</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.984117261599749e-06</v>
+        <v>0.002597899409011006</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001276563387364149</v>
+        <v>0.002653037896379828</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0006870566867291927</v>
+        <v>0.006792425643652678</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0008063999121077359</v>
+        <v>0.005726005416363478</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001785925589501858</v>
+        <v>0.0001277847040910274</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001665702555328608</v>
+        <v>0.0006762080593034625</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.656079494860023e-05</v>
+        <v>3.438035491853952e-06</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.29662871081382e-05</v>
+        <v>0.001902255811728537</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001077304361388087</v>
+        <v>0.0005203858599998057</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0016516731120646</v>
+        <v>0.0005313267465680838</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.001918324967846274</v>
+        <v>0.001885077217593789</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.003297940362244844</v>
+        <v>0.004110398702323437</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003289844375103712</v>
+        <v>0.0001801640028133988</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0009666398982517421</v>
+        <v>0.001143603236414492</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.000584135705139488</v>
+        <v>0.003479247447103262</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001463787513785064</v>
+        <v>0.0005265660001896322</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0008593573002144694</v>
+        <v>0.0003620001079980284</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001871611224487424</v>
+        <v>0.001133148092776537</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0008128627086989582</v>
+        <v>0.0006144733633846045</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0009569624089635909</v>
+        <v>0.001732198987156153</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002061070408672094</v>
+        <v>4.302072920836508e-05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0006780871190130711</v>
+        <v>0.0005865410203114152</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0008262897608801723</v>
+        <v>0.0003730510652530938</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0001708270283415914</v>
+        <v>0.0009679354261606932</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001120294095017016</v>
+        <v>0.00134757230989635</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0006570408586412668</v>
+        <v>5.882256664335728e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002874084748327732</v>
+        <v>0.001478523015975952</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0007678313413634896</v>
+        <v>0.001472837524488568</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001346546225249767</v>
+        <v>0.004194054286926985</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0005361441290006042</v>
+        <v>0.001658154069446027</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0004929578863084316</v>
+        <v>0.003296765265986323</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0004809880920220166</v>
+        <v>0.0003897140850313008</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001140901236794889</v>
+        <v>8.468813030049205e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0009415406966581941</v>
+        <v>0.001586529659107327</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0002522960712667555</v>
+        <v>0.0001865297672338784</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001320189447142184</v>
+        <v>0.001248373067937791</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0005746103124693036</v>
+        <v>0.0004924334352836013</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0005720659391954541</v>
+        <v>0.002197332680225372</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001323207834502682</v>
+        <v>8.190063817892224e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.093978400807828e-05</v>
+        <v>0.0009712274186313152</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001811248657759279</v>
+        <v>0.0005856407806277275</v>
       </c>
       <c r="CK9" t="n">
-        <v>2.05427932087332e-05</v>
+        <v>0.0009496991988271475</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0003857791889458895</v>
+        <v>0.0001792370894690976</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001397907733917236</v>
+        <v>7.132766768336296e-07</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0007717584376223385</v>
+        <v>2.638530713738874e-05</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0003864687168970704</v>
+        <v>0.00373164564371109</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001347895478829741</v>
+        <v>0.004247355274856091</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0001531684538349509</v>
+        <v>0.0006263407994993031</v>
       </c>
       <c r="CR9" t="n">
-        <v>5.622906610369682e-05</v>
+        <v>1.303973840549588e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001356498105451465</v>
+        <v>0.0007066974649205804</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.002394907176494598</v>
+        <v>0.002332651056349277</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001872421271400526</v>
+        <v>0.0005936506204307079</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0002739971969276667</v>
+        <v>0.000115485381684266</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001026964979246259</v>
+        <v>0.001004352234303951</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0007284329039976001</v>
+        <v>1.140902168117464e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0006991555565036833</v>
+        <v>0.002430845284834504</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0003545323561411351</v>
+        <v>0.0008878486696630716</v>
       </c>
       <c r="DA9" t="n">
-        <v>3.743480920093134e-05</v>
+        <v>0.001112707890570164</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0003523742780089378</v>
+        <v>0.0006608357653021812</v>
       </c>
       <c r="DC9" t="n">
-        <v>9.691226296126842e-05</v>
+        <v>0.0008010700112208724</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0002154782996512949</v>
+        <v>0.0003445370821282268</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0006021417793817818</v>
+        <v>9.156092710327357e-05</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0008053095662035048</v>
+        <v>0.00055115413852036</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0005242356564849615</v>
+        <v>0.001819504075683653</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002008233452215791</v>
+        <v>0.0004076051409356296</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001275648595765233</v>
+        <v>0.001295272028073668</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0006263367249630392</v>
+        <v>0.003257056698203087</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0004543918767012656</v>
+        <v>0.0002386752457823604</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0007651817868463695</v>
+        <v>0.005670462269335985</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001910360297188163</v>
+        <v>0.001398196094669402</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0005929999169893563</v>
+        <v>4.690123023465276e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001380140893161297</v>
+        <v>0.001155520440079272</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0008186724735423923</v>
+        <v>0.0001229436602443457</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0006838926346972585</v>
+        <v>0.0008893711492419243</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0003975371364504099</v>
+        <v>0.001021079951897264</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0002328821283299476</v>
+        <v>0.0001456773898098618</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001011830870993435</v>
+        <v>0.001072808867320418</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0003506936482153833</v>
+        <v>0.001945240539498627</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0004516436601988971</v>
+        <v>0.002804856514558196</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.50909909280017e-06</v>
+        <v>0.0002022871922235936</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0003142440982628614</v>
+        <v>0.0004555643536150455</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0007932493463158607</v>
+        <v>0.002017521765083075</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.949300975771621e-05</v>
+        <v>0.001545381615869701</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0005342981312423944</v>
+        <v>0.0002674507559277117</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001746527501381934</v>
+        <v>0.00220505241304636</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0001894921297207475</v>
+        <v>0.001166558591648936</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0007088918355293572</v>
+        <v>0.003446445101872087</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001197204110212624</v>
+        <v>0.003944212105125189</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0001095048792194575</v>
+        <v>0.001394864288158715</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0006744205020368099</v>
+        <v>0.0002231469843536615</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0002899813407566398</v>
+        <v>0.001900290488265455</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0007287904736585915</v>
+        <v>0.002066375687718391</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.000899928156286478</v>
+        <v>0.0001744937326293439</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.000121060358651448</v>
+        <v>0.0003362546267453581</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0004824499774258584</v>
+        <v>0.0002126767067238688</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003898876020684838</v>
+        <v>0.0003314364003017545</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0006990585825406015</v>
+        <v>0.0003756591468118131</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.000512712518684566</v>
+        <v>0.0007928848499432206</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001245506689883769</v>
+        <v>0.001983955968171358</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002197505964431912</v>
+        <v>3.945798380300403e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.000155554007505998</v>
+        <v>0.001780166523531079</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002331572177354246</v>
+        <v>5.435843922896311e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001650342484936118</v>
+        <v>0.0001474969612900168</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001369602745398879</v>
+        <v>0.00120515376329422</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0006105737993493676</v>
+        <v>0.0004921873332932591</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.000221060065086931</v>
+        <v>0.003003650112077594</v>
       </c>
       <c r="EX9" t="n">
-        <v>7.546126653323881e-06</v>
+        <v>0.000182300151209347</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001002485165372491</v>
+        <v>0.001230692840181291</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.000354497751686722</v>
+        <v>0.0003039279254153371</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0006150238332338631</v>
+        <v>0.002708795946091413</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0005412969621829689</v>
+        <v>0.0001336975255981088</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0002760827774181962</v>
+        <v>0.001043928437866271</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0004270995559636503</v>
+        <v>0.001046810299158096</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0002593329409137368</v>
+        <v>0.001083458540961146</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.422755303792655e-06</v>
+        <v>0.0003138424945063889</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0001052314401022159</v>
+        <v>0.000255241000559181</v>
       </c>
       <c r="FH9" t="n">
-        <v>4.510897269938141e-05</v>
+        <v>0.0006830477504990995</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001903041265904903</v>
+        <v>0.001011177431792021</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0003267778665758669</v>
+        <v>0.0008396962657570839</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0004917809856124222</v>
+        <v>0.000681790872476995</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0004993699258193374</v>
+        <v>0.0004726843326352537</v>
       </c>
       <c r="FM9" t="n">
-        <v>4.590973549056798e-05</v>
+        <v>0.0003646445402409881</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0001037952897604555</v>
+        <v>0.001459729042835534</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001681018329691142</v>
+        <v>0.002469227183610201</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0006626053364016116</v>
+        <v>0.002426198218017817</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0005835702759213746</v>
+        <v>0.002977005438879132</v>
       </c>
       <c r="FR9" t="n">
-        <v>5.551125286729075e-05</v>
+        <v>0.003598059294745326</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0008643326000310481</v>
+        <v>0.003223166801035404</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0004127036081627011</v>
+        <v>0.003524423111230135</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0005485928268171847</v>
+        <v>0.002084867795929313</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001009350758977234</v>
+        <v>0.0002687151136342436</v>
       </c>
       <c r="FW9" t="n">
-        <v>4.977014032192528e-05</v>
+        <v>0.007386697456240654</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001798512239474803</v>
+        <v>0.0001737779675750062</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.001129993819631636</v>
+        <v>0.0002935311058536172</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0005846951971761882</v>
+        <v>0.001639953814446926</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0004633198550436646</v>
+        <v>0.001111608697101474</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0009214146994054317</v>
+        <v>0.002694348338991404</v>
       </c>
       <c r="GC9" t="n">
-        <v>7.135216583264992e-05</v>
+        <v>0.0007773987017571926</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001489777350798249</v>
+        <v>0.002478508045896888</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.001660451875068247</v>
+        <v>0.001981114502996206</v>
       </c>
       <c r="GF9" t="n">
-        <v>9.542154293740168e-05</v>
+        <v>0.0008109488990157843</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0005872289184480906</v>
+        <v>0.001009718049317598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.04251489788293839</v>
+        <v>0.005482097156345844</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2423006445169449</v>
+        <v>0.01151525136083364</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02789902500808239</v>
+        <v>0.002390947192907333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07556769251823425</v>
+        <v>0.03289101272821426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0009601777419447899</v>
+        <v>0.007609501481056213</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03213744983077049</v>
+        <v>0.01282169762998819</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01841015182435513</v>
+        <v>0.01820115745067596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002876612357795238</v>
+        <v>0.01376792229712009</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01192282885313034</v>
+        <v>0.0109027000144124</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04923909157514572</v>
+        <v>0.005961287766695023</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1428493112325668</v>
+        <v>0.006548035424202681</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007023570593446493</v>
+        <v>0.002328505739569664</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1051209270954132</v>
+        <v>0.0439857505261898</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05558470636606216</v>
+        <v>0.02302076108753681</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06755297631025314</v>
+        <v>0.006685369648039341</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01895105093717575</v>
+        <v>0.01727809011936188</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01740138977766037</v>
+        <v>0.001674883533269167</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009920881129801273</v>
+        <v>0.00922175869345665</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01227108761668205</v>
+        <v>0.0004511484585236758</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04812834411859512</v>
+        <v>0.00416130106896162</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02914627455174923</v>
+        <v>0.001126563991419971</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02143140137195587</v>
+        <v>0.002213030122220516</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001703624613583088</v>
+        <v>0.002854437101632357</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03014373034238815</v>
+        <v>0.001556454924866557</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.00612952746450901</v>
+        <v>0.002856009174138308</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.003532582428306341</v>
+        <v>0.007188891526311636</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.003717474639415741</v>
+        <v>0.002735494868829846</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.02981670387089252</v>
+        <v>0.001414779806509614</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04738496989011765</v>
+        <v>0.008034936152398586</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01573318056762218</v>
+        <v>0.002903261221945286</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01445338875055313</v>
+        <v>0.001901748823001981</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01346507854759693</v>
+        <v>0.008031634613871574</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.00269220257177949</v>
+        <v>0.007697666995227337</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01985977217555046</v>
+        <v>0.00274052657186985</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.004226827528327703</v>
+        <v>0.0101573970168829</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.964663043618202e-05</v>
+        <v>0.00174524262547493</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03300519287586212</v>
+        <v>0.001839593169279397</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005215599667280912</v>
+        <v>0.005306679755449295</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.02399339154362679</v>
+        <v>0.0006551677943207324</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02660639397799969</v>
+        <v>0.003864589845761657</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02960055135190487</v>
+        <v>0.00126774434465915</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02062159031629562</v>
+        <v>0.002616733545437455</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.007045187056064606</v>
+        <v>0.008574190549552441</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0122629152610898</v>
+        <v>0.003740440821275115</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.009138390421867371</v>
+        <v>0.00169074023142457</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.009305204264819622</v>
+        <v>0.002522915601730347</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2025985419750214</v>
+        <v>0.001446679583750665</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01563918590545654</v>
+        <v>0.00501704029738903</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.01233190763741732</v>
+        <v>0.007477555423974991</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.05576442927122116</v>
+        <v>0.02953489869832993</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02285796962678432</v>
+        <v>0.0002526383323129267</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.007923061959445477</v>
+        <v>0.003111704252660275</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01140124350786209</v>
+        <v>0.00588523130863905</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.002863194094970822</v>
+        <v>0.003403248731046915</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0008444767445325851</v>
+        <v>0.006069766357541084</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04222434014081955</v>
+        <v>0.0005856616189703345</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.04364559426903725</v>
+        <v>0.003086883807554841</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.01819113828241825</v>
+        <v>0.005589426029473543</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.06943070888519287</v>
+        <v>0.007688791491091251</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.05406986549496651</v>
+        <v>0.000970518565736711</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0009438327979296446</v>
+        <v>0.006943723652511835</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.02206071093678474</v>
+        <v>0.01882906816899776</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.001746386988088489</v>
+        <v>0.001301842392422259</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.05984733626246452</v>
+        <v>0.0002228912780992687</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07222090661525726</v>
+        <v>0.004108710214495659</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.02018322609364986</v>
+        <v>0.002372398274019361</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.03316264972090721</v>
+        <v>0.01027225889265537</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03864966705441475</v>
+        <v>0.009295007213950157</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01157716754823923</v>
+        <v>0.005033614579588175</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.005112845450639725</v>
+        <v>0.004756774753332138</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.01759396493434906</v>
+        <v>0.002144799567759037</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.008320005610585213</v>
+        <v>0.002526701427996159</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01279967743903399</v>
+        <v>0.0005323898512870073</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.09418170899152756</v>
+        <v>0.005015905946493149</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.006432349793612957</v>
+        <v>0.00188500783406198</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01664326712489128</v>
+        <v>0.0199140626937151</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.02136643044650555</v>
+        <v>0.009139196015894413</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.05936441570520401</v>
+        <v>0.00162358011584729</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0162791945040226</v>
+        <v>0.002849212381988764</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.004380835220217705</v>
+        <v>0.001323841512203217</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.001293341396376491</v>
+        <v>0.004140661098062992</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0164252482354641</v>
+        <v>0.003088601632043719</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.04679057747125626</v>
+        <v>0.002547269221395254</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.004267035517841578</v>
+        <v>0.0003198554622940719</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.003012133063748479</v>
+        <v>0.01175874006003141</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0175008624792099</v>
+        <v>0.002168429549783468</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001522140693850815</v>
+        <v>0.004314997233450413</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.006790535058826208</v>
+        <v>0.004119952209293842</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.004082199186086655</v>
+        <v>0.002023551613092422</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.002209876431152225</v>
+        <v>0.001338578527793288</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.04848899319767952</v>
+        <v>0.008458804339170456</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.05277193337678909</v>
+        <v>0.005294226109981537</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02394843101501465</v>
+        <v>0.005857562646269798</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.06958396732807159</v>
+        <v>0.02262766659259796</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.03740890696644783</v>
+        <v>0.01083214860409498</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.04868000000715256</v>
+        <v>0.005780333653092384</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.01439353358000517</v>
+        <v>0.01522483117878437</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01173654943704605</v>
+        <v>0.002473219530656934</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004438825882971287</v>
+        <v>0.001432777848094702</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01746216788887978</v>
+        <v>0.003240077756345272</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0372447557747364</v>
+        <v>0.002048225607722998</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.007895324379205704</v>
+        <v>0.0004524387477431446</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01086444687098265</v>
+        <v>0.01338384114205837</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02230730280280113</v>
+        <v>0.002801415510475636</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.004809389356523752</v>
+        <v>0.003857493633404374</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.006148329004645348</v>
+        <v>0.00313320429995656</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.002318395301699638</v>
+        <v>0.0007716849213466048</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.003296527778729796</v>
+        <v>0.002027899026870728</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.005380838178098202</v>
+        <v>0.006091984454542398</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.03374380990862846</v>
+        <v>0.0002565016038715839</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0230444148182869</v>
+        <v>0.00810313131660223</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01108589209616184</v>
+        <v>0.0180766936391592</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.009497548453509808</v>
+        <v>0.002379488898441195</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.02410112321376801</v>
+        <v>0.005530622787773609</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01267407462000847</v>
+        <v>0.006568342447280884</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01250443235039711</v>
+        <v>0.01812901720404625</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0002239820605609566</v>
+        <v>0.00308538693934679</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.03497473150491714</v>
+        <v>0.003785834880545735</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01548373140394688</v>
+        <v>0.000730010389816016</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0295926108956337</v>
+        <v>0.004617907572537661</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.009211552329361439</v>
+        <v>0.009545553475618362</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.008862148970365524</v>
+        <v>0.0008121057762764394</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.01819067820906639</v>
+        <v>0.005414298269897699</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.00191396102309227</v>
+        <v>0.003618994727730751</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.00358618120662868</v>
+        <v>0.001052851090207696</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.00484205549582839</v>
+        <v>0.01352293696254492</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.00602441094815731</v>
+        <v>5.741871427744627e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.003051223931834102</v>
+        <v>0.002153572160750628</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.03367971256375313</v>
+        <v>0.009455864317715168</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.009085807017982006</v>
+        <v>0.001305387006141245</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02989338710904121</v>
+        <v>0.001761531224474311</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.00304604391567409</v>
+        <v>0.003403868991881609</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.002239534631371498</v>
+        <v>0.003831451293081045</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.002751945983618498</v>
+        <v>0.00889655202627182</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.003408901393413544</v>
+        <v>0.0004858244792558253</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.02484122850000858</v>
+        <v>0.007267843931913376</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.04630226269364357</v>
+        <v>0.0003014436224475503</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.01964435540139675</v>
+        <v>0.003226024331524968</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.005175752565264702</v>
+        <v>0.01056359615176916</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.006763368844985962</v>
+        <v>0.0050317058339715</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.009010830894112587</v>
+        <v>0.003310095751658082</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0005267939995974302</v>
+        <v>0.002822777722030878</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.009886408224701881</v>
+        <v>0.0005537011311389506</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.005341460928320885</v>
+        <v>0.0001520296791568398</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.02193501405417919</v>
+        <v>0.0007997178472578526</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.02907561883330345</v>
+        <v>0.005105955526232719</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01970846951007843</v>
+        <v>0.002007607370615005</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01978200115263462</v>
+        <v>0.01417445577681065</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02778644487261772</v>
+        <v>0.0001400298642693087</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.03507624939084053</v>
+        <v>0.006568255368620157</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0153428427875042</v>
+        <v>0.002930596005171537</v>
       </c>
       <c r="EV10" t="n">
-        <v>2.829940058290958e-05</v>
+        <v>0.001364590018056333</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.007212057709693909</v>
+        <v>0.005463102366775274</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01039291638880968</v>
+        <v>0.003243271494284272</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.04044263809919357</v>
+        <v>0.001697959960438311</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0003062861505895853</v>
+        <v>0.0003399615816306323</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.000905384193174541</v>
+        <v>0.01584563590586185</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.006890896707773209</v>
+        <v>0.00333647383376956</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.007986700162291527</v>
+        <v>0.003894176101312041</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.006026292219758034</v>
+        <v>0.002212546765804291</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.003765992121770978</v>
+        <v>0.001319006318226457</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.005200803279876709</v>
+        <v>0.001494454219937325</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01454248838126659</v>
+        <v>0.003991329111158848</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.002000549342483282</v>
+        <v>0.0002548856427893043</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.004418188706040382</v>
+        <v>0.001034252461977303</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01264160219579935</v>
+        <v>0.007436756510287523</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01575186103582382</v>
+        <v>0.002307750517502427</v>
       </c>
       <c r="FL10" t="n">
-        <v>4.204129800200462e-05</v>
+        <v>0.004018247127532959</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0108789736405015</v>
+        <v>0.001782801002264023</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0061683040112257</v>
+        <v>0.0036720996722579</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.006994318217039108</v>
+        <v>0.006125154439359903</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01853430457413197</v>
+        <v>0.009946675039827824</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.05304418504238129</v>
+        <v>0.01551216933876276</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.005494724027812481</v>
+        <v>0.003961133770644665</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.05732166394591331</v>
+        <v>0.004245778080075979</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.03374484181404114</v>
+        <v>0.009044166654348373</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.01122759096324444</v>
+        <v>0.01288540195673704</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.004178836941719055</v>
+        <v>0.006537151522934437</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.002742044162005186</v>
+        <v>0.005491738207638264</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.01100881025195122</v>
+        <v>0.007195804268121719</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.04121429845690727</v>
+        <v>0.001318541937507689</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02858726121485233</v>
+        <v>0.0004136167117394507</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.006733109708875418</v>
+        <v>0.007455988321453333</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.007687131408601999</v>
+        <v>0.01277454197406769</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.041758943349123</v>
+        <v>0.001508186454884708</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02246607840061188</v>
+        <v>0.00056914595188573</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.02241328917443752</v>
+        <v>0.002046292182058096</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.01704837195575237</v>
+        <v>0.0008386034751310945</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.002413426991552114</v>
+        <v>0.009207756258547306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.001464333385229111</v>
+        <v>0.0001599383249413222</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01682412251830101</v>
+        <v>0.00176243856549263</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001639077672734857</v>
+        <v>2.698157913982868e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004168602637946606</v>
+        <v>0.001107276882976294</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01411744672805071</v>
+        <v>0.0006148325628601015</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0005931508494541049</v>
+        <v>0.00232628732919693</v>
       </c>
       <c r="G11" t="n">
-        <v>4.836253356188536e-05</v>
+        <v>0.0004329920629970729</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003629937535151839</v>
+        <v>0.00128563679754734</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001043754047714174</v>
+        <v>4.875539889326319e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002462286269292235</v>
+        <v>0.0002486477314960212</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01410860754549503</v>
+        <v>0.002153895562514663</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001538803335279226</v>
+        <v>0.0003543830825947225</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0008286295342259109</v>
+        <v>0.0003988826938439161</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009895773604512215</v>
+        <v>0.001879048533737659</v>
       </c>
       <c r="O11" t="n">
-        <v>9.411427890881896e-05</v>
+        <v>0.002732059918344021</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0007529594004154205</v>
+        <v>4.181957046967e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0005708526587113738</v>
+        <v>0.0004079023492522538</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001483401283621788</v>
+        <v>0.000571671815123409</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003975718573201448</v>
+        <v>0.000457892834674567</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002547648502513766</v>
+        <v>0.0003104592033196241</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001376562868244946</v>
+        <v>0.0005954461521469057</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002528400626033545</v>
+        <v>0.0004133222391828895</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005918432958424091</v>
+        <v>0.0004347538051661104</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001007316051982343</v>
+        <v>0.0003961302281823009</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0002995738759636879</v>
+        <v>0.0002381831000093371</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.002684655133634806</v>
+        <v>0.0004239842528477311</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0005930202314630151</v>
+        <v>4.942407031194307e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.000243554706685245</v>
+        <v>0.0006871395744383335</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001009497325867414</v>
+        <v>0.0002717968309298158</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.00157367205247283</v>
+        <v>0.0001236286188941449</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0007298817508853972</v>
+        <v>0.000140504227601923</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.002072634873911738</v>
+        <v>0.00102124479599297</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0005694691790267825</v>
+        <v>0.000767001009080559</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.001989120384678245</v>
+        <v>0.000732309534214437</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0007738062413409352</v>
+        <v>0.001236911513842642</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.001002047443762422</v>
+        <v>0.0002213162370026112</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.002266441471874714</v>
+        <v>0.0003072069375775754</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.00300353835336864</v>
+        <v>0.0006350221810862422</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.002001452259719372</v>
+        <v>0.0004606529255397618</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.000520473113283515</v>
+        <v>0.0004466591926757246</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001399375032633543</v>
+        <v>0.0002682216290850192</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.002680595964193344</v>
+        <v>0.0002050149196293205</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0001783836632966995</v>
+        <v>9.865366155281663e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0004848236567340791</v>
+        <v>0.0002424518170300871</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0005382357630878687</v>
+        <v>0.0001224846346303821</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.001119209337048233</v>
+        <v>0.0001176381047116593</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.01261539943516254</v>
+        <v>0.002616065554320812</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0008838918292894959</v>
+        <v>0.0005246498039923608</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0001729805371724069</v>
+        <v>0.0001235738163813949</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.004164752550423145</v>
+        <v>0.0009417278924956918</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003639348782598972</v>
+        <v>0.00145311385858804</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.00331789767369628</v>
+        <v>0.0003991357225459069</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0001184709108201787</v>
+        <v>0.0002458317612763494</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.002536758314818144</v>
+        <v>0.0002466953301336616</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.002412888687103987</v>
+        <v>0.0006191892898641527</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.005697618238627911</v>
+        <v>0.0003500219609122723</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.042419509962201e-05</v>
+        <v>0.0001247668405994773</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.845188671723008e-05</v>
+        <v>0.001067747245542705</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.005554014351218939</v>
+        <v>1.571022585267201e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0002926500746980309</v>
+        <v>1.32257555378601e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.002497291658073664</v>
+        <v>0.0001755441626301035</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0001520111400168389</v>
+        <v>0.001169207273051143</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0009006751351989806</v>
+        <v>0.0003538975724950433</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.004064348060637712</v>
+        <v>0.0001494903117418289</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.00512280035763979</v>
+        <v>0.0008872429025359452</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.001417902298271656</v>
+        <v>9.611743735149503e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.001830869819968939</v>
+        <v>0.0002049477188847959</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.003450729418545961</v>
+        <v>0.0007137167849577963</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.00201197387650609</v>
+        <v>0.0009338109521195292</v>
       </c>
       <c r="BR11" t="n">
-        <v>8.816563058644533e-05</v>
+        <v>0.0003376987588126212</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.00163671572227031</v>
+        <v>8.71371739776805e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0004190693725831807</v>
+        <v>0.0006075652781873941</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.001621880102902651</v>
+        <v>0.0001162769767688587</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.008763907477259636</v>
+        <v>0.001619995338842273</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.00274207373149693</v>
+        <v>0.000260196888120845</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0005703261122107506</v>
+        <v>0.001122794346883893</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.001651839585974813</v>
+        <v>0.0002975796232931316</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.002752251690253615</v>
+        <v>0.0007665834855288267</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.001100976020097733</v>
+        <v>0.0001361973845632747</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0008495599613524973</v>
+        <v>0.0002139002463081852</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0004626301524695009</v>
+        <v>0.0003041643649339676</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0003897201386280358</v>
+        <v>0.0005960745038464665</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.002534861443564296</v>
+        <v>0.0006204716628417373</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0004049627168569714</v>
+        <v>0.0001980171509785578</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0009722747490741313</v>
+        <v>0.0001917392364703119</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.002154490444809198</v>
+        <v>5.20613684784621e-05</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0002050059556495398</v>
+        <v>0.0006297377403825521</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.00158372544683516</v>
+        <v>0.0001567959261592478</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0009723198018036783</v>
+        <v>8.708863606443629e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0001421450433554128</v>
+        <v>1.967786010936834e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.00392812816426158</v>
+        <v>0.0003683474496938288</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.004820228554308414</v>
+        <v>0.001256973948329687</v>
       </c>
       <c r="CO11" t="n">
-        <v>6.447982741519809e-05</v>
+        <v>0.0005460421089082956</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.001693642698228359</v>
+        <v>0.0006601976929232478</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.003504372434690595</v>
+        <v>0.0001617857633391395</v>
       </c>
       <c r="CR11" t="n">
-        <v>4.027027171105146e-05</v>
+        <v>4.916134639643133e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.00303883827291429</v>
+        <v>0.0004139145603403449</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.002246035728603601</v>
+        <v>0.0002223759365733713</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0001448231632821262</v>
+        <v>0.000107190542621538</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.681949990801513e-05</v>
+        <v>0.0004774050903506577</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.001824535895138979</v>
+        <v>0.0004524049290921539</v>
       </c>
       <c r="CX11" t="n">
-        <v>7.283337617991492e-05</v>
+        <v>6.542638584505767e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001476689008995891</v>
+        <v>6.679842772427946e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.00149733480066061</v>
+        <v>0.0001414525031577796</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0005644505145028234</v>
+        <v>0.0006589229451492429</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.001062091556377709</v>
+        <v>3.998857937403955e-05</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0009052968816831708</v>
+        <v>2.155566107830964e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>8.26621544547379e-06</v>
+        <v>1.963805698323995e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0008687445661053061</v>
+        <v>0.0002356592449359596</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.002712182234972715</v>
+        <v>0.0005441250978037715</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0007843765779398382</v>
+        <v>0.000207650096854195</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.009215017780661583</v>
+        <v>2.58384388871491e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.005796205252408981</v>
+        <v>0.0004795873537659645</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0002272632264066488</v>
+        <v>0.0001677324471529573</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.003257263917475939</v>
+        <v>0.000271405151579529</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0005065920413471758</v>
+        <v>0.001207946101203561</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.003673795377835631</v>
+        <v>0.001114672515541315</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0008686664514243603</v>
+        <v>0.0003836769610643387</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.001775798620656133</v>
+        <v>0.0001697411353234202</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0009576687589287758</v>
+        <v>6.386612949427217e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0004824619682040066</v>
+        <v>0.0005182800232432783</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.002365367487072945</v>
+        <v>0.0004048378323204815</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001697208732366562</v>
+        <v>0.0001629393373150378</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.000469489605166018</v>
+        <v>5.134512321092188e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0001650690392125398</v>
+        <v>0.0005458376836031675</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.001244233688339591</v>
+        <v>0.0001969532313523814</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0005923039861954749</v>
+        <v>0.0002536028623580933</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0009376584785059094</v>
+        <v>0.0001688228367129341</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001456865924410522</v>
+        <v>0.00028002675389871</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0001302901655435562</v>
+        <v>0.0002069439651677385</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0005537503166124225</v>
+        <v>0.0004016569000668824</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0002916670637205243</v>
+        <v>0.000485225667944178</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0004794448905158788</v>
+        <v>2.266891533508897e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.001105197938159108</v>
+        <v>0.0003210660652257502</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001765233697369695</v>
+        <v>0.001006187172606587</v>
       </c>
       <c r="EF11" t="n">
-        <v>7.212052878458053e-05</v>
+        <v>0.0003767360467463732</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.002139258431270719</v>
+        <v>8.691377297509462e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0002829509321600199</v>
+        <v>0.0004085850960109383</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0002106373431161046</v>
+        <v>9.654051245888695e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002004481386393309</v>
+        <v>0.0003765192232094705</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.001254835864529014</v>
+        <v>0.0005021525430493057</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0007460715714842081</v>
+        <v>2.53292455454357e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0007892393041402102</v>
+        <v>2.756821777438745e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0001253499649465084</v>
+        <v>4.186861042398959e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001572592300362885</v>
+        <v>0.000547373085282743</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0007877026800997555</v>
+        <v>0.000441377516835928</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001640414819121361</v>
+        <v>0.0001508228597231209</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.001787821645848453</v>
+        <v>8.716626325622201e-06</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001845257822424173</v>
+        <v>0.0006820383714511991</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.002383691957220435</v>
+        <v>0.0003279399825260043</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0007917779730632901</v>
+        <v>0.0001917098998092115</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.003082225332036614</v>
+        <v>0.0004905250389128923</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0003459119761828333</v>
+        <v>0.0001259408891201019</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001847460371209309</v>
+        <v>0.0006324568530544639</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.001520836958661675</v>
+        <v>0.0006154337315820158</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0002170673105865717</v>
+        <v>9.477147250436246e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.00101860542781651</v>
+        <v>0.0001321217423537746</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.00198303977958858</v>
+        <v>7.215475488919765e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0007709248457103968</v>
+        <v>0.0005333998706191778</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001638047862797976</v>
+        <v>0.0001633923384360969</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001067172037437558</v>
+        <v>2.34796607401222e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0005166417104192078</v>
+        <v>0.0002352376322960481</v>
       </c>
       <c r="FG11" t="n">
-        <v>5.405413685366511e-05</v>
+        <v>0.0001012363136396743</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.002116650342941284</v>
+        <v>0.0005016766372136772</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0002655903808772564</v>
+        <v>0.0001356296997983009</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.003154249861836433</v>
+        <v>0.0007243060972541571</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0006883976166136563</v>
+        <v>0.0002965849998872727</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0001439079351257533</v>
+        <v>0.0005566396284848452</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.001857048599049449</v>
+        <v>0.0004292854573577642</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001156809157691896</v>
+        <v>0.001142378663644195</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0002263061905978248</v>
+        <v>0.000519567693118006</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.002637071069329977</v>
+        <v>0.0002581650333013386</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001067430130206048</v>
+        <v>0.0009606175008229911</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0006632698932662606</v>
+        <v>0.000235980493016541</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.001626715529710054</v>
+        <v>0.000109291540866252</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.005359750241041183</v>
+        <v>0.0006790461484342813</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0007426530355587602</v>
+        <v>8.719146717339754e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.001314152148552239</v>
+        <v>0.0001036762405419722</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0010882169008255</v>
+        <v>0.001591489417478442</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.002244937233626842</v>
+        <v>0.0004866711387876421</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001575747039169073</v>
+        <v>0.0008470730972476304</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.001147776725701988</v>
+        <v>0.0001599956303834915</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.003171708667650819</v>
+        <v>0.0005861266981810331</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.001287956489250064</v>
+        <v>9.733786282595247e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0001142617256846279</v>
+        <v>0.000548584561329335</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.003287480445578694</v>
+        <v>0.0007504213135689497</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.002062787069007754</v>
+        <v>0.0001571967150084674</v>
       </c>
       <c r="GF11" t="n">
-        <v>9.038660209625959e-06</v>
+        <v>0.0001645838638069108</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0005484472494572401</v>
+        <v>0.0006657365593127906</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0003129625110886991</v>
+        <v>9.10415401449427e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003412106540054083</v>
+        <v>0.001219357131049037</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000315767916617915</v>
+        <v>0.0002397579082753509</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002379689365625381</v>
+        <v>0.001432897290214896</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0006407520268112421</v>
+        <v>0.0002694210561458021</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0005349352140910923</v>
+        <v>0.0008756212773732841</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0003605438687372953</v>
+        <v>0.0008676362922415137</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003508217632770538</v>
+        <v>0.0007533063180744648</v>
       </c>
       <c r="I12" t="n">
-        <v>7.032811117824167e-05</v>
+        <v>0.0003021773882210255</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000506808515638113</v>
+        <v>1.536233321530744e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.002263884525746107</v>
+        <v>0.0008973457152023911</v>
       </c>
       <c r="L12" t="n">
-        <v>2.368669811403379e-05</v>
+        <v>0.0003592382126953453</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00223161093890667</v>
+        <v>0.001996608218178153</v>
       </c>
       <c r="N12" t="n">
-        <v>0.001213983632624149</v>
+        <v>0.0008820079383440316</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001117321662604809</v>
+        <v>0.0008790234569460154</v>
       </c>
       <c r="P12" t="n">
-        <v>3.935056156478822e-05</v>
+        <v>0.000966064864769578</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0004000345943495631</v>
+        <v>0.0005035992944613099</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002810696023516357</v>
+        <v>0.0001715404796414077</v>
       </c>
       <c r="S12" t="n">
-        <v>8.567626355215907e-05</v>
+        <v>9.806458547245711e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0006095352000556886</v>
+        <v>3.011025182786398e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0001571598113514483</v>
+        <v>0.0001812335394788533</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0002650355745572597</v>
+        <v>0.0001111666861106642</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0001503139792475849</v>
+        <v>0.0003141021297778934</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0004072590672876686</v>
+        <v>0.0002790578582789749</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0004690331697929651</v>
+        <v>0.0001672411744948477</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0002149316569557413</v>
+        <v>0.0002436947543174028</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001533021422801539</v>
+        <v>3.539874887792394e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0002819692599587142</v>
+        <v>0.0001638847606955096</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0008447218569926918</v>
+        <v>2.341008803341538e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>8.407215500483289e-05</v>
+        <v>0.0002360257203690708</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0002247609518235549</v>
+        <v>0.000292459997581318</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0003211370785720646</v>
+        <v>0.000413948146160692</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0001793811243260279</v>
+        <v>0.0005685738869942725</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0004180044925305992</v>
+        <v>0.0003067684592679143</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0001582306867931038</v>
+        <v>0.0003249036672059447</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.69504764926387e-05</v>
+        <v>0.0001748615759424865</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0001732791715767235</v>
+        <v>9.967778896680102e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.000344545696862042</v>
+        <v>0.0004841228947043419</v>
       </c>
       <c r="AM12" t="n">
-        <v>5.918118040426634e-05</v>
+        <v>0.0003055977576877922</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0001988327276194468</v>
+        <v>0.0003321852418594062</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0004194510984234512</v>
+        <v>1.984123082365841e-05</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0004138653457630426</v>
+        <v>0.0002963233564514667</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001581374381203204</v>
+        <v>0.0002252382400911301</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0001709817152004689</v>
+        <v>8.215331035898998e-05</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.860385034698993e-05</v>
+        <v>5.812699600937776e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0003883039462380111</v>
+        <v>0.0004508210986386985</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.002622878178954124</v>
+        <v>0.000587543414440006</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.497927132732002e-05</v>
+        <v>0.0005162176676094532</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0001798150769900531</v>
+        <v>0.0002585764159448445</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0004585946444422007</v>
+        <v>0.001265527796931565</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0001584803976584226</v>
+        <v>0.0007811543764546514</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.282808655872941e-05</v>
+        <v>0.000131479580886662</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0002120393473887816</v>
+        <v>3.418299820623361e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.108910019975156e-05</v>
+        <v>0.000178409944055602</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.892570799100213e-05</v>
+        <v>1.066238473867998e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0004449232073966414</v>
+        <v>0.000285205605905503</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0006291468744166195</v>
+        <v>0.0001140256790677086</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0005932148778811097</v>
+        <v>0.0002400992525508627</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.001299128634855151</v>
+        <v>0.0005545427557080984</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0003568674437701702</v>
+        <v>1.78416958078742e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0006288690492510796</v>
+        <v>0.0002600374282337725</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.000292726734187454</v>
+        <v>0.0003127141389995813</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.000332866475218907</v>
+        <v>0.0001294677495025098</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0005870829918421805</v>
+        <v>0.0001443300570826977</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0006161787896417081</v>
+        <v>0.000195028173038736</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0002117245458066463</v>
+        <v>0.0001329883962171152</v>
       </c>
       <c r="BO12" t="n">
-        <v>2.238948945887387e-05</v>
+        <v>0.0003480172017589211</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0006113741546869278</v>
+        <v>0.0002105196035699919</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0002814666950143874</v>
+        <v>2.235736064903904e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0005579640856012702</v>
+        <v>2.475620749464724e-05</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0005085539305582643</v>
+        <v>1.524890194559703e-05</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.328316233819351e-05</v>
+        <v>5.652692561852746e-05</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0002422994584776461</v>
+        <v>0.0001547723077237606</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.001301362179219723</v>
+        <v>0.00056523981038481</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0003025513142347336</v>
+        <v>0.0002517173707019538</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0002281248162034899</v>
+        <v>0.0005272016278468072</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0001289037027163431</v>
+        <v>0.0002305084635736421</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0005393422907218337</v>
+        <v>0.000527587893884629</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.000136364862555638</v>
+        <v>0.0002969378256238997</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.746279303915799e-05</v>
+        <v>4.029616684420034e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001123694819398224</v>
+        <v>3.793787254835479e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0002046604931820184</v>
+        <v>3.440181899350137e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0006289409357123077</v>
+        <v>0.0002979861455969512</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0001657041138969362</v>
+        <v>6.656666664639488e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0001396931329509243</v>
+        <v>0.0005166203482076526</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0001696290564723313</v>
+        <v>7.12050314177759e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0001589352468727157</v>
+        <v>0.0001845945225795731</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0002607369096949697</v>
+        <v>4.380651807878166e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>2.254020364489406e-05</v>
+        <v>0.0001421583874616772</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0001212905626744032</v>
+        <v>8.860785601427779e-05</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0005597843555733562</v>
+        <v>0.0002989349304698408</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0003407874319236726</v>
+        <v>0.0001486626279074699</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0001799390447558835</v>
+        <v>0.0004840278998017311</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0009861924918368459</v>
+        <v>0.0005992078222334385</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0004604209680110216</v>
+        <v>0.0001119212392950431</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.000577980768866837</v>
+        <v>0.0001963247341336682</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0003545236540958285</v>
+        <v>0.0003421989677008241</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.000421284232288599</v>
+        <v>1.493108175054658e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>3.782297790166922e-05</v>
+        <v>0.0002009170420933515</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.000202751369215548</v>
+        <v>2.82105611404404e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0004778743896167725</v>
+        <v>0.000247802265221253</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0002277311577927321</v>
+        <v>8.853885810822248e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.00028971181018278</v>
+        <v>0.0005449443124234676</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.000153517205035314</v>
+        <v>0.000238721797359176</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0001929723657667637</v>
+        <v>0.0001967997814062983</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0002833851904142648</v>
+        <v>7.391930921585299e-06</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.364466490689665e-05</v>
+        <v>0.0001642194110900164</v>
       </c>
       <c r="DD12" t="n">
-        <v>7.220146653708071e-05</v>
+        <v>0.0001147044968092814</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0002266386582050472</v>
+        <v>0.0004206243611406535</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0006044814363121986</v>
+        <v>0.0002683782950043678</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.969260044163093e-05</v>
+        <v>6.6782595240511e-05</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.001015933463349938</v>
+        <v>0.0005670699756592512</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.000207391640287824</v>
+        <v>5.397766653914005e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0002075726224575192</v>
+        <v>0.001053574029356241</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0002410963352303952</v>
+        <v>0.0001236083335243165</v>
       </c>
       <c r="DL12" t="n">
-        <v>7.893634028732777e-05</v>
+        <v>0.0006235009641386569</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.000138752264319919</v>
+        <v>0.0004769740626215935</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.000351287453668192</v>
+        <v>0.0002052530471701175</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0002654538548085839</v>
+        <v>0.0003339758259244263</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0002829888835549355</v>
+        <v>2.109602064592764e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0003410667704883963</v>
+        <v>0.0001607232261449099</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0005416690255515277</v>
+        <v>0.0001882661890704185</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.000205097661819309</v>
+        <v>0.0002212181279901415</v>
       </c>
       <c r="DT12" t="n">
-        <v>9.261707600671798e-05</v>
+        <v>0.0001195188524434343</v>
       </c>
       <c r="DU12" t="n">
-        <v>3.088112862315029e-06</v>
+        <v>0.0002097866672556847</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001891386054921895</v>
+        <v>0.0005001997924409807</v>
       </c>
       <c r="DW12" t="n">
-        <v>4.806213837582618e-05</v>
+        <v>6.686207780148834e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>5.112467988510616e-05</v>
+        <v>0.0001023158474708907</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0004314797988627106</v>
+        <v>0.0004725510370917618</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0003570763510651886</v>
+        <v>0.0002757231122814119</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0004205647273920476</v>
+        <v>0.0001849311811383814</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0001148290539276786</v>
+        <v>0.0002401161182206124</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0001853142020991072</v>
+        <v>4.974595503881574e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0001537658972665668</v>
+        <v>0.000516088679432869</v>
       </c>
       <c r="EE12" t="n">
-        <v>4.068774433108047e-05</v>
+        <v>0.0003988900571130216</v>
       </c>
       <c r="EF12" t="n">
-        <v>9.758839587448165e-05</v>
+        <v>0.0001657587417867035</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0002531989011913538</v>
+        <v>0.0001383804192300886</v>
       </c>
       <c r="EH12" t="n">
-        <v>5.858272925252095e-05</v>
+        <v>0.0002086519380100071</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0001966168492799625</v>
+        <v>0.0005437048966996372</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.000460567040136084</v>
+        <v>0.0001108211072278209</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.000119413118227385</v>
+        <v>0.00013208226300776</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0005241149920038879</v>
+        <v>9.825137385632843e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0001400956971338019</v>
+        <v>1.571321627125144e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>4.504287790041417e-05</v>
+        <v>1.314585824729875e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.000215547886909917</v>
+        <v>2.282383502461016e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0005155857652425766</v>
+        <v>0.0003646408731583506</v>
       </c>
       <c r="EQ12" t="n">
-        <v>7.261784048750997e-05</v>
+        <v>5.671528560924344e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0002486092562321573</v>
+        <v>0.0004698145785368979</v>
       </c>
       <c r="ES12" t="n">
-        <v>9.302239050157368e-06</v>
+        <v>2.660450991243124e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0006463811732828617</v>
+        <v>1.470543793402612e-07</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.000454596389317885</v>
+        <v>0.0001603941345820203</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0001733250683173537</v>
+        <v>0.000217611639527604</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.404167414875701e-05</v>
+        <v>0.0003962234477512538</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0001148528317571618</v>
+        <v>3.397517139092088e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0004890586133114994</v>
+        <v>0.0003373727377038449</v>
       </c>
       <c r="EZ12" t="n">
-        <v>8.178557618521154e-05</v>
+        <v>4.594925121637061e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0002846560964826494</v>
+        <v>0.0005610938533209264</v>
       </c>
       <c r="FB12" t="n">
-        <v>7.581427053082734e-05</v>
+        <v>9.327055886387825e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0002605763729661703</v>
+        <v>0.0002329774579266086</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0002925499866250902</v>
+        <v>1.888589031295851e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>2.928785397671163e-05</v>
+        <v>0.0001528111315565184</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0001174596109194681</v>
+        <v>2.724147270782851e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>1.185275323223323e-06</v>
+        <v>0.000155762565555051</v>
       </c>
       <c r="FH12" t="n">
-        <v>9.179512562695891e-05</v>
+        <v>1.393428101437166e-05</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0001918741327244788</v>
+        <v>0.0001907949044834822</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0005453608464449644</v>
+        <v>0.0001171454932773486</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0002531186328269541</v>
+        <v>0.0001227356842719018</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0001646287855692208</v>
+        <v>6.70393492328003e-05</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0002338338526897132</v>
+        <v>0.0001608593738637865</v>
       </c>
       <c r="FN12" t="n">
-        <v>7.837361772544682e-05</v>
+        <v>7.946259574964643e-05</v>
       </c>
       <c r="FO12" t="n">
-        <v>8.094495569821447e-05</v>
+        <v>0.0002687019587028772</v>
       </c>
       <c r="FP12" t="n">
-        <v>7.181227556429803e-05</v>
+        <v>0.0002778655325528234</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0002032538031926379</v>
+        <v>0.0001445484667783603</v>
       </c>
       <c r="FR12" t="n">
-        <v>2.384378603892401e-06</v>
+        <v>0.0005485743167810142</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0004299432621337473</v>
+        <v>0.0001215972806676291</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0005995272658765316</v>
+        <v>0.0008589998469687998</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0001150105381384492</v>
+        <v>0.0001312197709921747</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0005553175578825176</v>
+        <v>0.0004465171659830958</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0003533823473844677</v>
+        <v>0.0007317858398891985</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0002158790011890233</v>
+        <v>0.0001535432529635727</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0004911751602776349</v>
+        <v>0.0001703630114207044</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.000207798948395066</v>
+        <v>5.741814675275236e-05</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0001099933360819705</v>
+        <v>0.0004153801710344851</v>
       </c>
       <c r="GB12" t="n">
-        <v>5.927006350248121e-05</v>
+        <v>0.0004338448052294552</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0005454639904201031</v>
+        <v>0.0002470983890816569</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.000295474601443857</v>
+        <v>0.0005566309555433691</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0008791518630459905</v>
+        <v>0.0003887610509991646</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.000195158994756639</v>
+        <v>5.557436088565737e-05</v>
       </c>
       <c r="GG12" t="n">
-        <v>9.395385859534144e-05</v>
+        <v>3.287997242296115e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01403607614338398</v>
+        <v>0.02424681186676025</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1087360754609108</v>
+        <v>0.1758107841014862</v>
       </c>
       <c r="C13" t="n">
-        <v>0.009872120805084705</v>
+        <v>0.009308302775025368</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0318862721323967</v>
+        <v>0.1289240121841431</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005812914576381445</v>
+        <v>0.03498925641179085</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09154751151800156</v>
+        <v>0.1076556295156479</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01303956285119057</v>
+        <v>0.08101903647184372</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04997906088829041</v>
+        <v>0.03961426764726639</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01224696822464466</v>
+        <v>0.01096658408641815</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02567052468657494</v>
+        <v>0.002149756997823715</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1025001779198647</v>
+        <v>0.2710232436656952</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00768771581351757</v>
+        <v>0.002649186179041862</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02385265566408634</v>
+        <v>0.1933827996253967</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02538271248340607</v>
+        <v>0.03887102752923965</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07474207878112793</v>
+        <v>0.1661586165428162</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01071706600487232</v>
+        <v>0.1113196834921837</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01658857986330986</v>
+        <v>0.0381927490234375</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02232781425118446</v>
+        <v>0.008428447879850864</v>
       </c>
       <c r="S13" t="n">
-        <v>0.002188296755775809</v>
+        <v>0.006562588736414909</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001386119751259685</v>
+        <v>0.03934476897120476</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003878438379615545</v>
+        <v>0.04608310014009476</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01388610620051622</v>
+        <v>0.1211786419153214</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0287920106202364</v>
+        <v>0.2449706047773361</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01796527579426765</v>
+        <v>0.1011267080903053</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.005184810608625412</v>
+        <v>0.05220994353294373</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01652464270591736</v>
+        <v>0.007386587560176849</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01113217324018478</v>
+        <v>0.05996204167604446</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001230922061949968</v>
+        <v>0.078077033162117</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0009169727563858032</v>
+        <v>0.02433236688375473</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.003397394437342882</v>
+        <v>0.003400703892111778</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.007392512634396553</v>
+        <v>0.002123381942510605</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01863095909357071</v>
+        <v>0.05800596997141838</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01676213182508945</v>
+        <v>0.1121784150600433</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001810025656595826</v>
+        <v>0.05238689482212067</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.005952771287411451</v>
+        <v>0.05434178933501244</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0001590067404322326</v>
+        <v>0.08748698979616165</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01688608527183533</v>
+        <v>0.03162302821874619</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.00443194480612874</v>
+        <v>0.0289301797747612</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.005324836820363998</v>
+        <v>0.001160442596301436</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01016936637461185</v>
+        <v>0.08161096274852753</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0004680064739659429</v>
+        <v>0.0615151934325695</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01388103980571032</v>
+        <v>0.03270871192216873</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.003631269093602896</v>
+        <v>0.003740780055522919</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.007715517189353704</v>
+        <v>0.09424102306365967</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.006535529624670744</v>
+        <v>0.0435696542263031</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.003387823700904846</v>
+        <v>0.04758903384208679</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.05936626344919205</v>
+        <v>0.3796121776103973</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.004973194096237421</v>
+        <v>0.03934798762202263</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.01372963190078735</v>
+        <v>0.07208578288555145</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0004181732074357569</v>
+        <v>0.007174346596002579</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.04951106011867523</v>
+        <v>0.07860701531171799</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02261560782790184</v>
+        <v>0.09626273065805435</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.009244000539183617</v>
+        <v>0.08520278334617615</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.01534429378807545</v>
+        <v>0.05629946291446686</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003519448451697826</v>
+        <v>0.0403159037232399</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04341525584459305</v>
+        <v>0.0632472038269043</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.02664756029844284</v>
+        <v>0.04857856780290604</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004769529215991497</v>
+        <v>0.0558634027838707</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001704132184386253</v>
+        <v>0.01154331117868423</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01958558335900307</v>
+        <v>0.08799876272678375</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.009477830491960049</v>
+        <v>0.1264023333787918</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.001975198509171605</v>
+        <v>0.03230537474155426</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01523694209754467</v>
+        <v>0.004465041682124138</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01233150251209736</v>
+        <v>0.04217030480504036</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02458829432725906</v>
+        <v>0.0531933568418026</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01401076279580593</v>
+        <v>0.002989174798130989</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.005872976500540972</v>
+        <v>0.05599082261323929</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.01579894870519638</v>
+        <v>3.237556666135788e-05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.001984771806746721</v>
+        <v>0.009115381166338921</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0007309969514608383</v>
+        <v>0.1414822041988373</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.004348226822912693</v>
+        <v>0.02941882610321045</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.003565716790035367</v>
+        <v>0.044206153601408</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0001008401159197092</v>
+        <v>0.03526278585195541</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03962487354874611</v>
+        <v>0.1800016909837723</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.007341212593019009</v>
+        <v>0.02828974649310112</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.006344819441437721</v>
+        <v>0.1541807502508163</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.003677638713270426</v>
+        <v>0.2224698066711426</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.02385694719851017</v>
+        <v>0.1529814004898071</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.001736222067847848</v>
+        <v>0.03721224516630173</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.00130320293828845</v>
+        <v>0.03522119671106339</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.007794370874762535</v>
+        <v>0.07805212587118149</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.002131649293005466</v>
+        <v>0.02293778397142887</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01738650724291801</v>
+        <v>0.06212232634425163</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01006383076310158</v>
+        <v>0.00164338480681181</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.001714881509542465</v>
+        <v>0.01874621585011482</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0004250456113368273</v>
+        <v>0.01389112137258053</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01535584405064583</v>
+        <v>0.05563590675592422</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.007109561003744602</v>
+        <v>0.04583968967199326</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.008468830958008766</v>
+        <v>0.01691945269703865</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.008198320865631104</v>
+        <v>0.009134034626185894</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01716239750385284</v>
+        <v>0.09515658020973206</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02039799280464649</v>
+        <v>0.2098549902439117</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001041683135554194</v>
+        <v>0.002663627965375781</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.02502284571528435</v>
+        <v>0.04452025145292282</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.006543857045471668</v>
+        <v>0.1394554674625397</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.005250866059213877</v>
+        <v>0.1792270839214325</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.01752031408250332</v>
+        <v>0.0528697595000267</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01430705189704895</v>
+        <v>0.09861323982477188</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.00564892590045929</v>
+        <v>0.08366942405700684</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001602161210030317</v>
+        <v>0.03271534666419029</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01521926932036877</v>
+        <v>0.05467626079916954</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.009162822738289833</v>
+        <v>0.0002233460545539856</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.005520922131836414</v>
+        <v>0.005671963095664978</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.002823573537170887</v>
+        <v>0.005984606221318245</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01465258561074734</v>
+        <v>0.032160434871912</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.006756312679499388</v>
+        <v>0.02631681226193905</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.01233868859708309</v>
+        <v>0.02120057120919228</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.004990003071725368</v>
+        <v>0.001359016634523869</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001506091910414398</v>
+        <v>0.006031835917383432</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.007840557955205441</v>
+        <v>0.05153235048055649</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.001175031764432788</v>
+        <v>0.05883048474788666</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.05093200877308846</v>
+        <v>0.03101135790348053</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01605938374996185</v>
+        <v>0.03261709213256836</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03327003121376038</v>
+        <v>0.08094947040081024</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.009203291498124599</v>
+        <v>0.06191451475024223</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.02255414798855782</v>
+        <v>0.009679912589490414</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02007914148271084</v>
+        <v>0.1451068520545959</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.001297092414461076</v>
+        <v>0.02468345314264297</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.008420102298259735</v>
+        <v>0.01855676993727684</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01665383204817772</v>
+        <v>0.002024440327659249</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.00962568074464798</v>
+        <v>0.1481451988220215</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0125831663608551</v>
+        <v>0.04738457128405571</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.007278430741280317</v>
+        <v>0.04290932416915894</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.002768032252788544</v>
+        <v>0.02866499125957489</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.00284394365735352</v>
+        <v>0.08723260462284088</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.003340921830385923</v>
+        <v>0.002389619126915932</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0002148924395442009</v>
+        <v>0.03741865605115891</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.005813999101519585</v>
+        <v>0.03362384811043739</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.002561195753514767</v>
+        <v>0.03553193062543869</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.003386253025382757</v>
+        <v>0.1056591272354126</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.004285401664674282</v>
+        <v>0.05184819176793098</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01889926567673683</v>
+        <v>0.07376238703727722</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0004729956854134798</v>
+        <v>0.01761128380894661</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.008531998842954636</v>
+        <v>0.07322649657726288</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01986522227525711</v>
+        <v>0.007563721388578415</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.001458365470170975</v>
+        <v>0.03056793846189976</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0180673785507679</v>
+        <v>0.0234665684401989</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.007562373764812946</v>
+        <v>0.007530603557825089</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.003833804279565811</v>
+        <v>0.07675682008266449</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.003405505791306496</v>
+        <v>0.0430961474776268</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.005042953882366419</v>
+        <v>0.002731839194893837</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.004531074780970812</v>
+        <v>0.002363209612667561</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.004329167772084475</v>
+        <v>0.007819871418178082</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.005355229135602713</v>
+        <v>0.03728415071964264</v>
       </c>
       <c r="EO13" t="n">
-        <v>5.750847049057484e-05</v>
+        <v>0.007888390682637691</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01018342934548855</v>
+        <v>0.002733077388256788</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.001219599042087793</v>
+        <v>0.01870867982506752</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.00647845771163702</v>
+        <v>0.01146278716623783</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.00330467545427382</v>
+        <v>0.04624883085489273</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01559440046548843</v>
+        <v>0.05649182200431824</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.01403280720114708</v>
+        <v>0.02252957224845886</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.03752502799034119</v>
+        <v>0.04517271369695663</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.008437143638730049</v>
+        <v>0.00897732749581337</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001241326332092285</v>
+        <v>0.03168156370520592</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01162684336304665</v>
+        <v>0.07333681732416153</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.005217673722654581</v>
+        <v>0.000303557375445962</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001022951444610953</v>
+        <v>0.006218826398253441</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001362217590212822</v>
+        <v>0.000817522406578064</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.01305970549583435</v>
+        <v>0.04984849318861961</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.01183964870870113</v>
+        <v>0.05155143141746521</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.009933061897754669</v>
+        <v>0.0206836573779583</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.007736097555607557</v>
+        <v>0.009847385808825493</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.00728378351777792</v>
+        <v>0.03402474150061607</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.006905063055455685</v>
+        <v>0.090552918612957</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.003650485537946224</v>
+        <v>0.02964149788022041</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01859870553016663</v>
+        <v>0.06338810920715332</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.004107199143618345</v>
+        <v>0.01396366953849792</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.004690754227340221</v>
+        <v>0.0611611045897007</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.009594359435141087</v>
+        <v>0.03483842313289642</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.004320805426687002</v>
+        <v>0.02054331451654434</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.002876986283808947</v>
+        <v>0.002573415637016296</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.009373394772410393</v>
+        <v>0.03347785770893097</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01665741577744484</v>
+        <v>0.2339335232973099</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01119532994925976</v>
+        <v>0.003178451675921679</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.006272909231483936</v>
+        <v>0.1032995507121086</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02406060695648193</v>
+        <v>0.1673381626605988</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01790121011435986</v>
+        <v>0.04950258880853653</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01367571391165257</v>
+        <v>0.1187310293316841</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.007109038531780243</v>
+        <v>0.004117760807275772</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01225168071687222</v>
+        <v>0.07440123707056046</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01566393673419952</v>
+        <v>0.005188168026506901</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.008002376183867455</v>
+        <v>0.01004247553646564</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.004916778765618801</v>
+        <v>0.0326249971985817</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.00703592412173748</v>
+        <v>0.008038804866373539</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.006633547134697437</v>
+        <v>0.1082771718502045</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.00514977378770709</v>
+        <v>0.04917792975902557</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.02742679789662361</v>
+        <v>0.02051472850143909</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.005227140616625547</v>
+        <v>0.006810631603002548</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.002243146300315857</v>
+        <v>0.04167510196566582</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0001124438422266394</v>
+        <v>0.00624841870740056</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001633270061574876</v>
+        <v>0.02936692349612713</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001999466912820935</v>
+        <v>0.005008853506296873</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0007824086351320148</v>
+        <v>0.03924544528126717</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004533594183158129</v>
+        <v>0.0006473223911598325</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003194150340277702</v>
+        <v>0.0128410654142499</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001368434750474989</v>
+        <v>0.01963735744357109</v>
       </c>
       <c r="H14" t="n">
-        <v>3.44509280694183e-05</v>
+        <v>0.01444567181169987</v>
       </c>
       <c r="I14" t="n">
-        <v>9.29358066059649e-05</v>
+        <v>0.001861635013483465</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001406350929755718</v>
+        <v>0.002869872841984034</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001209277426823974</v>
+        <v>0.03369558975100517</v>
       </c>
       <c r="L14" t="n">
-        <v>6.119013414718211e-05</v>
+        <v>0.0004108487628400326</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0006186060491017997</v>
+        <v>0.05423984304070473</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0004673823423217982</v>
+        <v>0.008640808053314686</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0003139000327792019</v>
+        <v>0.01786854676902294</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001151088072219864</v>
+        <v>0.0155916903167963</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0003343450371176004</v>
+        <v>0.00293845240958035</v>
       </c>
       <c r="R14" t="n">
-        <v>4.012584759038873e-05</v>
+        <v>0.001822998514398932</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001093601968022995</v>
+        <v>0.002579220337793231</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0002507893950678408</v>
+        <v>0.001721031847409904</v>
       </c>
       <c r="U14" t="n">
-        <v>7.45756333344616e-05</v>
+        <v>0.003549636574462056</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0002249465032946318</v>
+        <v>0.006141600664705038</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0001192779382108711</v>
+        <v>0.007116961292922497</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000165527846547775</v>
+        <v>0.009855014272034168</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001442179782316089</v>
+        <v>0.005125888623297215</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001569322630530223</v>
+        <v>0.007458433974534273</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001083507740986533</v>
+        <v>0.002484684344381094</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.690541780088097e-05</v>
+        <v>0.001696777530014515</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.024667835736182e-05</v>
+        <v>0.00394463911652565</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.954604032216594e-05</v>
+        <v>0.001912584761157632</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.926320121332537e-05</v>
+        <v>0.01424347329884768</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.232531915069558e-05</v>
+        <v>0.007912885397672653</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.023291305406019e-05</v>
+        <v>0.0102770859375596</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.939608359360136e-05</v>
+        <v>0.00393938971683383</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0001700184657238424</v>
+        <v>0.01178612187504768</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.693306148808915e-05</v>
+        <v>0.007461551111191511</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0002293517463840544</v>
+        <v>0.0008789660641923547</v>
       </c>
       <c r="AL14" t="n">
-        <v>7.567298598587513e-05</v>
+        <v>0.005651597864925861</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.901446557894815e-05</v>
+        <v>0.006437378935515881</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001515022740932181</v>
+        <v>0.01136399246752262</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0001833455316955224</v>
+        <v>0.000107466010376811</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0002024996792897582</v>
+        <v>0.007038277573883533</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.072739390423521e-05</v>
+        <v>0.0002629365772008896</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0001285153848584741</v>
+        <v>0.004905757959932089</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.254550968762487e-05</v>
+        <v>0.002301229629665613</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.995675458805636e-06</v>
+        <v>0.002041789935901761</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001023946213535964</v>
+        <v>0.0262355450540781</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.654139850870706e-05</v>
+        <v>0.004588908050209284</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.466782699339092e-05</v>
+        <v>0.01628710515797138</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.839023752836511e-05</v>
+        <v>0.02814589813351631</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.100684261880815e-05</v>
+        <v>0.01217075902968645</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.000128711893921718</v>
+        <v>0.001598280388861895</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0002675168216228485</v>
+        <v>0.005338723305612803</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.9877210080449e-06</v>
+        <v>0.004690487403422594</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.513337525073439e-05</v>
+        <v>0.004314678721129894</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0002193203690694645</v>
+        <v>0.009148850105702877</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0003757904923986644</v>
+        <v>0.002981138648465276</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0002467268786858767</v>
+        <v>0.003383316099643707</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0006003621965646744</v>
+        <v>0.02361815050244331</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0001528721040813252</v>
+        <v>0.003917086869478226</v>
       </c>
       <c r="BI14" t="n">
-        <v>8.364942914340645e-06</v>
+        <v>0.002470307052135468</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002783692034427077</v>
+        <v>0.01495619211345911</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.539100412628613e-05</v>
+        <v>0.006087284069508314</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001666660973569378</v>
+        <v>0.002598808379843831</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0003119407629128546</v>
+        <v>0.01042064465582371</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0001014916488202289</v>
+        <v>0.003033958841115236</v>
       </c>
       <c r="BO14" t="n">
-        <v>8.99765745998593e-06</v>
+        <v>0.004647432826459408</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0002239066234324127</v>
+        <v>0.007581183686852455</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0001634489017305896</v>
+        <v>0.003563048550859094</v>
       </c>
       <c r="BR14" t="n">
-        <v>8.574061212129891e-07</v>
+        <v>0.01133812870830297</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0001219090772792697</v>
+        <v>0.005030449014157057</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.334971137926914e-05</v>
+        <v>0.003489060793071985</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.493127537192777e-05</v>
+        <v>0.000580473046284169</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0005452228942885995</v>
+        <v>0.01078318245708942</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0001814802380977198</v>
+        <v>0.005364288575947285</v>
       </c>
       <c r="BX14" t="n">
-        <v>5.449262971524149e-05</v>
+        <v>0.01732758060097694</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.369792011653772e-06</v>
+        <v>0.004730895161628723</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0002064176223939285</v>
+        <v>0.01048782933503389</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.000176181347342208</v>
+        <v>0.008467243984341621</v>
       </c>
       <c r="CB14" t="n">
-        <v>1.600620089448057e-05</v>
+        <v>0.00216201483272016</v>
       </c>
       <c r="CC14" t="n">
-        <v>6.048769591870951e-06</v>
+        <v>0.002997615840286016</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.257598862343002e-05</v>
+        <v>0.0008193603134714067</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0002724120568018407</v>
+        <v>0.008795594796538353</v>
       </c>
       <c r="CF14" t="n">
-        <v>9.851194045040756e-05</v>
+        <v>0.001214411808177829</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.00010324932372896</v>
+        <v>0.01250661909580231</v>
       </c>
       <c r="CH14" t="n">
-        <v>6.908949580974877e-05</v>
+        <v>0.003053002525120974</v>
       </c>
       <c r="CI14" t="n">
-        <v>7.86297969170846e-05</v>
+        <v>0.0002967974869534373</v>
       </c>
       <c r="CJ14" t="n">
-        <v>6.300301902228966e-05</v>
+        <v>0.001458313316106796</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.385726035456173e-05</v>
+        <v>0.002081391401588917</v>
       </c>
       <c r="CL14" t="n">
-        <v>7.79696274548769e-05</v>
+        <v>6.602087523788214e-06</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0003013892273884267</v>
+        <v>0.01142918691039085</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.05561809707433e-05</v>
+        <v>0.01934347674250603</v>
       </c>
       <c r="CO14" t="n">
-        <v>9.883558959700167e-05</v>
+        <v>0.01684309728443623</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0001989957672776654</v>
+        <v>0.02288141846656799</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0001801335311029106</v>
+        <v>0.005760177969932556</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.000370112102245912</v>
+        <v>0.004638588987290859</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0001795457064872608</v>
+        <v>0.007148450240492821</v>
       </c>
       <c r="CT14" t="n">
-        <v>9.269330621464178e-05</v>
+        <v>0.005851383320987225</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0001601197145646438</v>
+        <v>0.004549412522464991</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.195812365040183e-05</v>
+        <v>0.0001474932359997183</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0002461670665070415</v>
+        <v>0.008386099711060524</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0001089155048248358</v>
+        <v>0.0002836271887645125</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0001547034044051543</v>
+        <v>0.01484943740069866</v>
       </c>
       <c r="CZ14" t="n">
-        <v>5.773715383838862e-05</v>
+        <v>0.002435536589473486</v>
       </c>
       <c r="DA14" t="n">
-        <v>7.515306788263842e-05</v>
+        <v>0.0004552928148768842</v>
       </c>
       <c r="DB14" t="n">
-        <v>8.201288437703624e-05</v>
+        <v>0.001199895050376654</v>
       </c>
       <c r="DC14" t="n">
-        <v>8.98138532647863e-05</v>
+        <v>0.002248264849185944</v>
       </c>
       <c r="DD14" t="n">
-        <v>5.775881436420605e-05</v>
+        <v>0.0003824808809440583</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001296056143473834</v>
+        <v>0.002993425354361534</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0004007472889497876</v>
+        <v>0.002873100806027651</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0001617125089978799</v>
+        <v>0.005317057948559523</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.000501236179843545</v>
+        <v>0.01033314689993858</v>
       </c>
       <c r="DI14" t="n">
-        <v>1.12676734715933e-05</v>
+        <v>0.002773689338937402</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0001175781872007065</v>
+        <v>0.0007172852056100965</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.990633144392632e-05</v>
+        <v>0.004196163266897202</v>
       </c>
       <c r="DL14" t="n">
-        <v>3.857334377244115e-05</v>
+        <v>0.01940164715051651</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001195987715618685</v>
+        <v>0.007368908263742924</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0001787299843272194</v>
+        <v>0.003069602651521564</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001173968048533425</v>
+        <v>0.009404824115335941</v>
       </c>
       <c r="DP14" t="n">
-        <v>1.787524888641201e-05</v>
+        <v>0.002331559546291828</v>
       </c>
       <c r="DQ14" t="n">
-        <v>6.774235953344032e-05</v>
+        <v>0.003359634429216385</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.52125124563463e-05</v>
+        <v>0.002372619463130832</v>
       </c>
       <c r="DS14" t="n">
-        <v>8.965715824160725e-05</v>
+        <v>0.003893898334354162</v>
       </c>
       <c r="DT14" t="n">
-        <v>9.058813884621486e-05</v>
+        <v>0.008717594668269157</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001212269926327281</v>
+        <v>0.008173037320375443</v>
       </c>
       <c r="DV14" t="n">
-        <v>8.026084105949849e-05</v>
+        <v>0.008152118884027004</v>
       </c>
       <c r="DW14" t="n">
-        <v>1.285023608943447e-05</v>
+        <v>0.003945642616599798</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001091758240363561</v>
+        <v>0.00294481823220849</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0001785732456482947</v>
+        <v>0.004367986228317022</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.41023005603347e-05</v>
+        <v>0.007225085981190205</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0002021545951720327</v>
+        <v>0.00971781462430954</v>
       </c>
       <c r="EB14" t="n">
-        <v>5.242181941866875e-06</v>
+        <v>0.001173634198494256</v>
       </c>
       <c r="EC14" t="n">
-        <v>8.980993879958987e-05</v>
+        <v>0.0009354919893667102</v>
       </c>
       <c r="ED14" t="n">
-        <v>3.795915108639747e-05</v>
+        <v>0.02356816455721855</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.000161909352755174</v>
+        <v>0.01010123174637556</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0002130462089553475</v>
+        <v>0.002446746919304132</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0002707005478441715</v>
+        <v>0.001518901321105659</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0001267968764295802</v>
+        <v>0.003702754620462656</v>
       </c>
       <c r="EI14" t="n">
-        <v>9.304397826781496e-05</v>
+        <v>0.008697434328496456</v>
       </c>
       <c r="EJ14" t="n">
-        <v>8.9599983766675e-05</v>
+        <v>0.002431677654385567</v>
       </c>
       <c r="EK14" t="n">
-        <v>6.712778122164309e-05</v>
+        <v>0.001645353157073259</v>
       </c>
       <c r="EL14" t="n">
-        <v>9.970516839530319e-05</v>
+        <v>9.977573063224554e-05</v>
       </c>
       <c r="EM14" t="n">
-        <v>4.881913991994224e-05</v>
+        <v>0.001626600394956768</v>
       </c>
       <c r="EN14" t="n">
-        <v>2.598078390292358e-05</v>
+        <v>0.001541920471936464</v>
       </c>
       <c r="EO14" t="n">
-        <v>4.391715629026294e-05</v>
+        <v>0.001086530275642872</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.000116809198516421</v>
+        <v>0.006811469793319702</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001001084019662812</v>
+        <v>0.001517893630079925</v>
       </c>
       <c r="ER14" t="n">
-        <v>7.904442463768646e-05</v>
+        <v>0.01181728672236204</v>
       </c>
       <c r="ES14" t="n">
-        <v>8.522830466972664e-05</v>
+        <v>0.001956288237124681</v>
       </c>
       <c r="ET14" t="n">
-        <v>5.522632272914052e-05</v>
+        <v>0.008298998698592186</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0001642115094000474</v>
+        <v>0.007139422930777073</v>
       </c>
       <c r="EV14" t="n">
-        <v>5.002279431209899e-05</v>
+        <v>0.0008956908714026213</v>
       </c>
       <c r="EW14" t="n">
-        <v>7.427381206071004e-05</v>
+        <v>0.01012598443776369</v>
       </c>
       <c r="EX14" t="n">
-        <v>4.543714749161154e-05</v>
+        <v>0.0002988988999277353</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0002479884424246848</v>
+        <v>0.009626044891774654</v>
       </c>
       <c r="EZ14" t="n">
-        <v>8.651620009914041e-05</v>
+        <v>0.001276278402656317</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0001191378541989252</v>
+        <v>0.01560378819704056</v>
       </c>
       <c r="FB14" t="n">
-        <v>2.413440415693913e-05</v>
+        <v>0.001266705337911844</v>
       </c>
       <c r="FC14" t="n">
-        <v>7.914796151453629e-05</v>
+        <v>0.001842463854700327</v>
       </c>
       <c r="FD14" t="n">
-        <v>8.595063991378993e-05</v>
+        <v>0.003810428082942963</v>
       </c>
       <c r="FE14" t="n">
-        <v>6.052262324374169e-05</v>
+        <v>0.004140595439821482</v>
       </c>
       <c r="FF14" t="n">
-        <v>9.63918209890835e-05</v>
+        <v>0.0007125824922695756</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001044367527356371</v>
+        <v>0.003148757386952639</v>
       </c>
       <c r="FH14" t="n">
-        <v>5.215180499362759e-05</v>
+        <v>0.001904831500723958</v>
       </c>
       <c r="FI14" t="n">
-        <v>8.152725786203519e-05</v>
+        <v>0.002131517045199871</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0001864798250608146</v>
+        <v>0.007024575024843216</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0001815971336327493</v>
+        <v>0.006224364973604679</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0001706892799120396</v>
+        <v>0.00243880832567811</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0001007463797577657</v>
+        <v>0.003537991549819708</v>
       </c>
       <c r="FN14" t="n">
-        <v>7.222293061204255e-05</v>
+        <v>0.004191113635897636</v>
       </c>
       <c r="FO14" t="n">
-        <v>4.178054041403811e-06</v>
+        <v>0.00471449876204133</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001145483402069658</v>
+        <v>0.01301166601479053</v>
       </c>
       <c r="FQ14" t="n">
-        <v>8.306595191243105e-06</v>
+        <v>0.008506881073117256</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0002839273365680128</v>
+        <v>0.01351157203316689</v>
       </c>
       <c r="FS14" t="n">
-        <v>7.040636774036102e-06</v>
+        <v>0.007914922200143337</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0002501684648450464</v>
+        <v>0.002833592006936669</v>
       </c>
       <c r="FU14" t="n">
-        <v>8.935244295571465e-06</v>
+        <v>0.001509721390902996</v>
       </c>
       <c r="FV14" t="n">
-        <v>6.698093784507364e-05</v>
+        <v>0.006905787158757448</v>
       </c>
       <c r="FW14" t="n">
-        <v>9.740761743159965e-05</v>
+        <v>0.008107922039926052</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002025828580372036</v>
+        <v>0.002793374005705118</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0002013892080867663</v>
+        <v>0.002041181549429893</v>
       </c>
       <c r="FZ14" t="n">
-        <v>4.404429637361318e-05</v>
+        <v>0.002801710506901145</v>
       </c>
       <c r="GA14" t="n">
-        <v>3.908809594577178e-05</v>
+        <v>0.004204696044325829</v>
       </c>
       <c r="GB14" t="n">
-        <v>5.17638836754486e-05</v>
+        <v>0.01332799717783928</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0001545249397167936</v>
+        <v>0.004585227929055691</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001349743688479066</v>
+        <v>0.006929645780473948</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0002520157722756267</v>
+        <v>0.02030489034950733</v>
       </c>
       <c r="GF14" t="n">
-        <v>9.75124494289048e-05</v>
+        <v>0.0009017261327244341</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.000206576703931205</v>
+        <v>0.001683311304077506</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.03494318574666977</v>
+        <v>0.01186860352754593</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2568027079105377</v>
+        <v>0.7517921924591064</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09842588752508163</v>
+        <v>0.1611369997262955</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09082060307264328</v>
+        <v>0.2369575649499893</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01652312837541103</v>
+        <v>0.1689811795949936</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05895711854100227</v>
+        <v>0.2762500643730164</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008867204189300537</v>
+        <v>0.2554521560668945</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0464850515127182</v>
+        <v>0.3735094666481018</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05431710928678513</v>
+        <v>0.05423751845955849</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1142530590295792</v>
+        <v>0.1370396614074707</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2245977371931076</v>
+        <v>0.8370581269264221</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09179127961397171</v>
+        <v>0.2037703394889832</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1419716626405716</v>
+        <v>0.4704563617706299</v>
       </c>
       <c r="N15" t="n">
-        <v>0.005370592698454857</v>
+        <v>0.2885448634624481</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04654005542397499</v>
+        <v>0.04115443676710129</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04716670513153076</v>
+        <v>0.2773047089576721</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.06477448344230652</v>
+        <v>0.4186306595802307</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08006494492292404</v>
+        <v>0.02866639569401741</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01036641746759415</v>
+        <v>0.005239678546786308</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05741884559392929</v>
+        <v>0.01933866739273071</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03068005293607712</v>
+        <v>0.006041822023689747</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04214766249060631</v>
+        <v>0.008563905954360962</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01846923679113388</v>
+        <v>0.03464154154062271</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01370079070329666</v>
+        <v>0.03049443103373051</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0008192993700504303</v>
+        <v>0.05291413888335228</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.01330837234854698</v>
+        <v>0.05613855645060539</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02948497608304024</v>
+        <v>0.1703788936138153</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05350223183631897</v>
+        <v>0.0939599797129631</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.05102772265672684</v>
+        <v>0.1197218373417854</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01006294786930084</v>
+        <v>0.07379830628633499</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.001698387786746025</v>
+        <v>0.1394830495119095</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.002708869520574808</v>
+        <v>0.04027162492275238</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.003525363281369209</v>
+        <v>0.09573385119438171</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.01471503078937531</v>
+        <v>0.09567467123270035</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.00115263694897294</v>
+        <v>0.05194241181015968</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.01898290775716305</v>
+        <v>0.07905448228120804</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01741647534072399</v>
+        <v>0.07546016573905945</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04301922768354416</v>
+        <v>0.2087825834751129</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0001939113717526197</v>
+        <v>0.1237931996583939</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03295940160751343</v>
+        <v>0.04254209995269775</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02271086908876896</v>
+        <v>0.1493291705846786</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.05041303485631943</v>
+        <v>0.00534908939152956</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.02436891570687294</v>
+        <v>0.05203793942928314</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.01143833622336388</v>
+        <v>0.009824380278587341</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.02659420482814312</v>
+        <v>0.02662848681211472</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.06503108143806458</v>
+        <v>0.01429052650928497</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1414822638034821</v>
+        <v>0.3396335542201996</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.03344548866152763</v>
+        <v>0.02356982976198196</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.01006081327795982</v>
+        <v>0.1575339287519455</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0009060557931661606</v>
+        <v>0.223508432507515</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.04606163501739502</v>
+        <v>0.06355567276477814</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.008164763450622559</v>
+        <v>0.03963612765073776</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.01523764804005623</v>
+        <v>0.0493769645690918</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.05727101489901543</v>
+        <v>0.03187756240367889</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0700359046459198</v>
+        <v>0.02100343629717827</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05032461509108543</v>
+        <v>0.04693929105997086</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.04405993968248367</v>
+        <v>0.101141169667244</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.04554465413093567</v>
+        <v>0.03178991377353668</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1561349332332611</v>
+        <v>0.05893554538488388</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0400298535823822</v>
+        <v>0.1136332452297211</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.02514874935150146</v>
+        <v>0.002451192587614059</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.1294440627098083</v>
+        <v>0.1004394218325615</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.01369185373187065</v>
+        <v>0.06455666571855545</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.04330501332879066</v>
+        <v>0.0712733268737793</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.01303734444081783</v>
+        <v>0.08138062059879303</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.03764014318585396</v>
+        <v>0.06437721848487854</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.009822784923017025</v>
+        <v>0.008772943168878555</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.04555395245552063</v>
+        <v>0.02666768990457058</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01347743440419436</v>
+        <v>0.002407865133136511</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.05509859323501587</v>
+        <v>0.1068715527653694</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.02736460231244564</v>
+        <v>0.04404290392994881</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.02424224652349949</v>
+        <v>0.07253507524728775</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.05777021497488022</v>
+        <v>0.04362995177507401</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.06635595858097076</v>
+        <v>0.1961692273616791</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.004631602205336094</v>
+        <v>0.04293582588434219</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02471592649817467</v>
+        <v>0.06970877945423126</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.05766387656331062</v>
+        <v>0.02939784713089466</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01556774415075779</v>
+        <v>0.05465862154960632</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.01848145574331284</v>
+        <v>0.08546844869852066</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.02759451232850552</v>
+        <v>0.0149009358137846</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0570630244910717</v>
+        <v>0.08376772701740265</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.03255303576588631</v>
+        <v>0.005811973474919796</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.042939443141222</v>
+        <v>0.2340841144323349</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.01378081552684307</v>
+        <v>0.0461677722632885</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02117042429745197</v>
+        <v>0.05976890027523041</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.03731071576476097</v>
+        <v>0.05208677425980568</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.02543141506612301</v>
+        <v>0.1074939072132111</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.003727675415575504</v>
+        <v>0.01577781699597836</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.005766758695244789</v>
+        <v>0.06061645969748497</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.01352972816675901</v>
+        <v>0.01087832543998957</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.007720625959336758</v>
+        <v>0.03842056542634964</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.003381127258762717</v>
+        <v>0.126897782087326</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.007119919173419476</v>
+        <v>0.07923106849193573</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.007829655893146992</v>
+        <v>0.05853669717907906</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.06527624279260635</v>
+        <v>0.2324313074350357</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.006709508132189512</v>
+        <v>0.1270254701375961</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.02758048474788666</v>
+        <v>0.1583333909511566</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.02733047306537628</v>
+        <v>0.1460456103086472</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.02450166083872318</v>
+        <v>0.01498160418123007</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.02635145746171474</v>
+        <v>0.003196774050593376</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.04046443477272987</v>
+        <v>0.2276272922754288</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.006237007677555084</v>
+        <v>0.03085517697036266</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.01883348263800144</v>
+        <v>0.0868169292807579</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.02721097506582737</v>
+        <v>0.06970983743667603</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01651804521679878</v>
+        <v>0.1185334026813507</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0156053826212883</v>
+        <v>0.02347970753908157</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.003350947052240372</v>
+        <v>0.0661998987197876</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.01112892758101225</v>
+        <v>0.02020956389605999</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.01789113879203796</v>
+        <v>0.0266981665045023</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1448971778154373</v>
+        <v>0.05966469645500183</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.006074516102671623</v>
+        <v>0.07477285712957382</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.01332692615687847</v>
+        <v>0.1129163652658463</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0003764235880225897</v>
+        <v>0.00266745314002037</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.08463684469461441</v>
+        <v>0.4883294999599457</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.03974441066384315</v>
+        <v>0.0693683996796608</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01431789807975292</v>
+        <v>0.04827245324850082</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0169109795242548</v>
+        <v>0.1089682430028915</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.04733498767018318</v>
+        <v>0.01156922988593578</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.03058468736708164</v>
+        <v>0.1588228046894073</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1185735762119293</v>
+        <v>0.05316432565450668</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.04721410572528839</v>
+        <v>0.04504145309329033</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.05869325622916222</v>
+        <v>0.04626816511154175</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0369071327149868</v>
+        <v>0.02936296537518501</v>
       </c>
       <c r="DT15" t="n">
-        <v>6.272015161812305e-05</v>
+        <v>0.0468912310898304</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.01378413382917643</v>
+        <v>0.01693720370531082</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.004541466012597084</v>
+        <v>0.1563318818807602</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.02098728716373444</v>
+        <v>0.02181864157319069</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.008773650042712688</v>
+        <v>0.0907115563750267</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.06602649390697479</v>
+        <v>0.05212660133838654</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.04378286376595497</v>
+        <v>0.05801674723625183</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02581683918833733</v>
+        <v>0.1324679255485535</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.08368606865406036</v>
+        <v>0.2759404480457306</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.02154126949608326</v>
+        <v>0.05128359794616699</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.04211214929819107</v>
+        <v>0.1813128590583801</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.02438989281654358</v>
+        <v>0.0564611591398716</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.050189308822155</v>
+        <v>0.02548296377062798</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.03352946788072586</v>
+        <v>0.2517115473747253</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0001269539352506399</v>
+        <v>0.054465651512146</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.005280307494103909</v>
+        <v>0.02320390753448009</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.009450402110815048</v>
+        <v>0.01134668570011854</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01047143805772066</v>
+        <v>0.1175093427300453</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.0005744732916355133</v>
+        <v>0.02111559361219406</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.01875763759016991</v>
+        <v>0.08788148313760757</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.01798714324831963</v>
+        <v>0.03664384782314301</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.00446044746786356</v>
+        <v>0.1114562377333641</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.03332507610321045</v>
+        <v>0.2164785265922546</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.004599102772772312</v>
+        <v>0.01954032480716705</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.02474150992929935</v>
+        <v>0.1808700114488602</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01834310032427311</v>
+        <v>0.1210496202111244</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.001724839326925576</v>
+        <v>0.001392075791954994</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.04460279271006584</v>
+        <v>0.122834175825119</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.02983934618532658</v>
+        <v>0.1044186875224113</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.00170029466971755</v>
+        <v>0.03947579860687256</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.02054281905293465</v>
+        <v>0.004151701927185059</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.05564869940280914</v>
+        <v>0.274482250213623</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.01480082795023918</v>
+        <v>0.04232130572199821</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0223697368055582</v>
+        <v>0.06880287826061249</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01817759498953819</v>
+        <v>0.04735096544027328</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01558137498795986</v>
+        <v>0.1103840246796608</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.02384990081191063</v>
+        <v>0.01584495231509209</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.007026690989732742</v>
+        <v>0.0749901607632637</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.02454354614019394</v>
+        <v>0.02663783729076385</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.001470913179218769</v>
+        <v>0.03921375423669815</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.03298581019043922</v>
+        <v>0.09240712225437164</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.009627423249185085</v>
+        <v>0.06972628831863403</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0002094903029501438</v>
+        <v>0.01483378373086452</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.03406622633337975</v>
+        <v>0.07985422760248184</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.05530911311507225</v>
+        <v>0.01339930389076471</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.006014418788254261</v>
+        <v>0.04426122829318047</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.002938360907137394</v>
+        <v>0.06761419773101807</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.02557847835123539</v>
+        <v>0.1309845894575119</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.1149787306785583</v>
+        <v>0.197630301117897</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.04938660562038422</v>
+        <v>0.1246655434370041</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.09746694564819336</v>
+        <v>0.1942097246646881</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.02831599675118923</v>
+        <v>0.4940125346183777</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.06092151626944542</v>
+        <v>0.146462082862854</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.05667600780725479</v>
+        <v>0.1601732820272446</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.04254664480686188</v>
+        <v>0.2563872635364532</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0113258957862854</v>
+        <v>0.1320453435182571</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.03796681761741638</v>
+        <v>0.04958747327327728</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.04722126945853233</v>
+        <v>0.05399083346128464</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.009019334800541401</v>
+        <v>0.06693009287118912</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.006994926836341619</v>
+        <v>0.0495428703725338</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.02582068741321564</v>
+        <v>0.03208504989743233</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.05057394877076149</v>
+        <v>0.09759407490491867</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.05878428742289543</v>
+        <v>0.1019978150725365</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.05854736268520355</v>
+        <v>0.03142645210027695</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0120912678539753</v>
+        <v>0.1365099251270294</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.007612193934619427</v>
+        <v>0.03305027261376381</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.003122250782325864</v>
+        <v>0.0009792068740352988</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001060692593455315</v>
+        <v>0.0004299861320760101</v>
       </c>
       <c r="C16" t="n">
-        <v>0.007656083442270756</v>
+        <v>0.003126374678686261</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005461010150611401</v>
+        <v>0.004345870576798916</v>
       </c>
       <c r="E16" t="n">
-        <v>0.003796289674937725</v>
+        <v>3.389635821804404e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001213032053783536</v>
+        <v>0.0005596933769993484</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001409268355928361</v>
+        <v>0.00131889502517879</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001075378269888461</v>
+        <v>0.0008079087710939348</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0008759572519920766</v>
+        <v>0.002376694232225418</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003070877399295568</v>
+        <v>0.0003386603493709117</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0008334156009368598</v>
+        <v>0.001143573550507426</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005654086824506521</v>
+        <v>0.003037090878933668</v>
       </c>
       <c r="M16" t="n">
-        <v>0.005805108696222305</v>
+        <v>0.004892070777714252</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0003965740324929357</v>
+        <v>0.001677049556747079</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001460616011172533</v>
+        <v>0.0003249430446885526</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0006061343592591584</v>
+        <v>0.0007204998400993645</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0005987468757666647</v>
+        <v>0.002497612731531262</v>
       </c>
       <c r="R16" t="n">
-        <v>0.002177402609959245</v>
+        <v>0.0007036057650111616</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005092000355944037</v>
+        <v>0.0002453408960718662</v>
       </c>
       <c r="T16" t="n">
-        <v>0.000808730605058372</v>
+        <v>0.0004379471647553146</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0008844350231811404</v>
+        <v>0.000888100010342896</v>
       </c>
       <c r="V16" t="n">
-        <v>0.001511476119048893</v>
+        <v>0.001989430980756879</v>
       </c>
       <c r="W16" t="n">
-        <v>0.001380833215080202</v>
+        <v>0.001368857687339187</v>
       </c>
       <c r="X16" t="n">
-        <v>3.854032911476679e-05</v>
+        <v>0.0009717013454064727</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0008754830923862755</v>
+        <v>0.0005072022322565317</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001063671428710222</v>
+        <v>0.0001397308515151963</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0006529350066557527</v>
+        <v>0.0004830015823245049</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.002263350877910852</v>
+        <v>0.0006799695547670126</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0006761293625459075</v>
+        <v>0.0001163543784059584</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0004621455154847354</v>
+        <v>5.175104888621718e-06</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.001256722141988575</v>
+        <v>0.002409363631159067</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.001301085692830384</v>
+        <v>0.001380209228955209</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.854147507809103e-05</v>
+        <v>0.0006522578769363463</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0002362725499551743</v>
+        <v>1.014670124277472e-05</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.001154929166659713</v>
+        <v>0.001197924837470055</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.001112639554776251</v>
+        <v>0.0009684998076409101</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.000269665673840791</v>
+        <v>0.0002200695162173361</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0005133282393217087</v>
+        <v>0.0001169934548670426</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.000192754901945591</v>
+        <v>0.0009300512028858066</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0005950834602117538</v>
+        <v>0.001836963230744004</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.001645459095016122</v>
+        <v>0.001722692511975765</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0004152668407186866</v>
+        <v>0.00100790336728096</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.000952965347096324</v>
+        <v>0.001320973387919366</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.734089114004746e-05</v>
+        <v>0.0002539397100917995</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0008430920424871147</v>
+        <v>0.0007771018426865339</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.002087749540805817</v>
+        <v>0.000269514333922416</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.002392280614003539</v>
+        <v>0.0004424545913934708</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.004890996497124434</v>
+        <v>0.004165080841630697</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.004608780611306429</v>
+        <v>0.003701417008414865</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.001374727580696344</v>
+        <v>0.0001147581497207284</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.001872024615295231</v>
+        <v>0.002822712995111942</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.00108850235119462</v>
+        <v>0.002150869462639093</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.001516596763394773</v>
+        <v>0.001179052283987403</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.00108018540777266</v>
+        <v>0.001219607307575643</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.002090901602059603</v>
+        <v>0.002132095163688064</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.002819298300892115</v>
+        <v>0.0004152885812800378</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0005684290081262589</v>
+        <v>0.0005586871993727982</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.001553205773234367</v>
+        <v>0.002363588660955429</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.002512026578187943</v>
+        <v>0.0004941726219840348</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.002028004266321659</v>
+        <v>0.002508864272385836</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.001509188557974994</v>
+        <v>0.001902396907098591</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.001023142132908106</v>
+        <v>0.0007169508608058095</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.001850210013799369</v>
+        <v>0.0009852905059233308</v>
       </c>
       <c r="BL16" t="n">
-        <v>4.998083750251681e-05</v>
+        <v>8.449546294286847e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.001277611125260592</v>
+        <v>0.0003334012872073799</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0003677065251395106</v>
+        <v>0.0003744855639524758</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.209622031543404e-05</v>
+        <v>0.0007837737794034183</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.001518260687589645</v>
+        <v>0.0005416510393843055</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.63605605950579e-05</v>
+        <v>0.0009120915783569217</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0004697596887126565</v>
+        <v>0.0003924726624973118</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0009580436162650585</v>
+        <v>0.001592211076058447</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0006978156743571162</v>
+        <v>0.0001947216223925352</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.0002386866544838995</v>
+        <v>4.54990949947387e-05</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.001900976989418268</v>
+        <v>7.534268661402166e-06</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.003323799464851618</v>
+        <v>0.002749361097812653</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.002877789083868265</v>
+        <v>0.005591375753283501</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.001299850409850478</v>
+        <v>0.0006885909824632108</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.000380291196051985</v>
+        <v>0.0006767039885744452</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0003322979318909347</v>
+        <v>0.0007466146489605308</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.001488745445385575</v>
+        <v>0.0003105653158854693</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0009230300784111023</v>
+        <v>0.000385935214580968</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.00106175581458956</v>
+        <v>0.0002231860271422192</v>
       </c>
       <c r="CE16" t="n">
-        <v>7.244714652188122e-06</v>
+        <v>0.0004216767265461385</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.001809147419407964</v>
+        <v>0.00086415238911286</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0006699205841869116</v>
+        <v>0.00156950275413692</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0006641446962021291</v>
+        <v>0.0002182448224630207</v>
       </c>
       <c r="CI16" t="n">
-        <v>7.216434460133314e-05</v>
+        <v>0.0001071552542271093</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0005087422905489802</v>
+        <v>0.0001306963240494952</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0004635545774362981</v>
+        <v>0.0003933666739612818</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0002051609626505524</v>
+        <v>0.0002687087398953736</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.00259612943045795</v>
+        <v>0.0001466800604248419</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.003304267767816782</v>
+        <v>0.0001562080287840217</v>
       </c>
       <c r="CO16" t="n">
-        <v>2.019142266362906e-05</v>
+        <v>0.001969211036339402</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0008568607154302299</v>
+        <v>0.001621069153770804</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.001625008648261428</v>
+        <v>0.001125695882365108</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.001016316702589393</v>
+        <v>0.0001192372001241893</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0006219534552656114</v>
+        <v>0.0003332943888381124</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.002745214384049177</v>
+        <v>0.000136469941935502</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0002906001463998109</v>
+        <v>0.001638207701034844</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0008948736358433962</v>
+        <v>0.0004746986669488251</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0005038253148086369</v>
+        <v>6.519228918477893e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.001173877855762839</v>
+        <v>0.0007161459070630372</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0008022409747354686</v>
+        <v>0.001627698773518205</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0002895636134780943</v>
+        <v>0.0001163168490165845</v>
       </c>
       <c r="DA16" t="n">
-        <v>7.692736107856035e-05</v>
+        <v>0.000434563058661297</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0003966707154177129</v>
+        <v>9.209883864969015e-05</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0003665697295218706</v>
+        <v>0.0003362176066730171</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.21343429479748e-07</v>
+        <v>0.0003106598742306232</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0009583803475834429</v>
+        <v>0.001048308564350009</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.003119503380730748</v>
+        <v>0.0005879372474737465</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.001678917673416436</v>
+        <v>0.001024856814183295</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.001378182088956237</v>
+        <v>0.00157844799105078</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0007871136767789721</v>
+        <v>0.0006525212666019797</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.001084984396584332</v>
+        <v>0.001063347910530865</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.002692441223189235</v>
+        <v>0.001733199926093221</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0006629989948123693</v>
+        <v>0.001971963560208678</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0008871259051375091</v>
+        <v>0.0007210633484646678</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.0001262039877474308</v>
+        <v>0.0003436806728132069</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.001375315245240927</v>
+        <v>0.0004792890103999525</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.001314122346229851</v>
+        <v>0.0001128654839703813</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0004974527982994914</v>
+        <v>0.0008664525812491775</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.001970215933397412</v>
+        <v>0.001217874465510249</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.001168207149021327</v>
+        <v>0.0004559405206236988</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.0007794973789714277</v>
+        <v>0.001030163140967488</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0003164805530104786</v>
+        <v>0.0007144577102735639</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.001872617402113974</v>
+        <v>0.001546087558381259</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.020164927467704e-05</v>
+        <v>0.001188736176118255</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.001850697910413146</v>
+        <v>0.0004257327236700803</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0003824403102044016</v>
+        <v>0.0004683363367803395</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.000948938715737313</v>
+        <v>0.000292884767986834</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0004511073348112404</v>
+        <v>5.284653161652386e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.001958390465006232</v>
+        <v>0.0004424965591169894</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.0001484988024458289</v>
+        <v>0.0009061184246093035</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0003882026067003608</v>
+        <v>0.0007332669338211417</v>
       </c>
       <c r="EE16" t="n">
-        <v>6.970565300434828e-05</v>
+        <v>0.0004672842333093286</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0004095276235602796</v>
+        <v>7.284249295480549e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0009572376729920506</v>
+        <v>2.962799044325948e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.001785761676728725</v>
+        <v>0.0004455737071111798</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.002042160835117102</v>
+        <v>0.00127445999532938</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0001105162518797442</v>
+        <v>0.001292885397560894</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001222917053382844</v>
+        <v>0.0001270171196665615</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0004798879963345826</v>
+        <v>3.880274380207993e-05</v>
       </c>
       <c r="EM16" t="n">
-        <v>2.475811197655275e-05</v>
+        <v>1.818292366806418e-05</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.0008002764079719782</v>
+        <v>2.066962770186365e-05</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.0002538973931223154</v>
+        <v>8.750747656449676e-05</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.001451458549126983</v>
+        <v>0.0009170794510282576</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0008270229445770383</v>
+        <v>0.0008193087996914983</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0008949736948125064</v>
+        <v>0.001368355704471469</v>
       </c>
       <c r="ES16" t="n">
-        <v>5.593829700956121e-05</v>
+        <v>0.0005247393273748457</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0003745655994862318</v>
+        <v>0.001315968227572739</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0002590344520285726</v>
+        <v>0.0001692073128651828</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0002334390883333981</v>
+        <v>0.001676269574090838</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0007812709081918001</v>
+        <v>0.0003285368147771806</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.0008586136973462999</v>
+        <v>0.0003243897226639092</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0005527847679331899</v>
+        <v>0.0003844900638796389</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.001489999471232295</v>
+        <v>0.001001322292722762</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0007714933017268777</v>
+        <v>0.001883967663161457</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0004671999777201563</v>
+        <v>0.0003637250338215381</v>
       </c>
       <c r="FC16" t="n">
-        <v>6.272425525821745e-05</v>
+        <v>0.0001962597307283431</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0002681765472516418</v>
+        <v>0.0001118709114962257</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.000126545928651467</v>
+        <v>0.0006974395364522934</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0004837588348891586</v>
+        <v>0.0002287552633788437</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.000891499686986208</v>
+        <v>6.148693501017988e-05</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.001191430725157261</v>
+        <v>0.0008964876760728657</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0002740856725722551</v>
+        <v>0.001417485764250159</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.001216256408952177</v>
+        <v>0.001106044044718146</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0008764463127590716</v>
+        <v>0.0007031317218206823</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0008593687089160085</v>
+        <v>0.0001211994094774127</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0005325847887434065</v>
+        <v>0.0001876887399703264</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0007860485929995775</v>
+        <v>0.0001399549510097131</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.001215243013575673</v>
+        <v>0.0004417062446009368</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.001198749872855842</v>
+        <v>5.641730967909098e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.001044598291628063</v>
+        <v>0.0005754018784500659</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.002317424630746245</v>
+        <v>0.0009546331129968166</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.0003934386768378317</v>
+        <v>7.254362571984529e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0001700753346085548</v>
+        <v>0.0004842188209295273</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0004645233566407114</v>
+        <v>0.002188857179135084</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.000693847774527967</v>
+        <v>0.0008906579460017383</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0004601848195306957</v>
+        <v>0.0001384661591146141</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.0006772388005629182</v>
+        <v>0.001355115557089448</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.000175317152752541</v>
+        <v>0.0001901187642943114</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.001093094935640693</v>
+        <v>9.291242167819291e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0004586161812767386</v>
+        <v>0.0003690367157105356</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0006318652885966003</v>
+        <v>0.001231157220900059</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.00171164283528924</v>
+        <v>0.0006314940401352942</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.002241038018837571</v>
+        <v>0.0001788991503417492</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0005824885447509587</v>
+        <v>0.0003732136392500252</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0009909895015880466</v>
+        <v>3.091379767283797e-05</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0001480994251323864</v>
+        <v>0.0008963545551523566</v>
       </c>
     </row>
   </sheetData>
